--- a/GameData/GameData_Enemy.xlsx
+++ b/GameData/GameData_Enemy.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D796F03A-3947-4844-954C-1076582F7DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E244986-7CEF-4639-A408-986440C24232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="1080" windowWidth="20360" windowHeight="13180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="1080" windowWidth="20360" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Boss" sheetId="4" r:id="rId1"/>
-    <sheet name="Goblin Mage" sheetId="3" r:id="rId2"/>
-    <sheet name="Skeleton" sheetId="1" r:id="rId3"/>
+    <sheet name="ex" sheetId="5" r:id="rId1"/>
+    <sheet name="Boss" sheetId="4" r:id="rId2"/>
+    <sheet name="Goblin Mage" sheetId="3" r:id="rId3"/>
+    <sheet name="Skeleton" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t>스켈레톤</t>
   </si>
@@ -110,6 +111,10 @@
   </si>
   <si>
     <t>성장식 (x=LV)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>스켈레톤</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -277,7 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -286,6 +291,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -542,6 +550,555 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B8B626-F353-4976-AFFB-A1371686E86A}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="22" customHeight="1">
+      <c r="A2" s="5"/>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>20</v>
+      </c>
+      <c r="D2" s="17">
+        <v>20</v>
+      </c>
+      <c r="E2" s="18">
+        <v>0.81</v>
+      </c>
+      <c r="F2" s="16">
+        <v>1</v>
+      </c>
+      <c r="G2" s="17">
+        <v>5</v>
+      </c>
+      <c r="H2" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="22" customHeight="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="16">
+        <v>26</v>
+      </c>
+      <c r="D3" s="17">
+        <v>25</v>
+      </c>
+      <c r="E3" s="18">
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="F3" s="16">
+        <v>1</v>
+      </c>
+      <c r="G3" s="17">
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="H3" s="16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="22" customHeight="1">
+      <c r="A4" s="5"/>
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="16">
+        <v>36</v>
+      </c>
+      <c r="D4" s="17">
+        <v>27.9</v>
+      </c>
+      <c r="E4" s="18">
+        <v>0.83000000000000007</v>
+      </c>
+      <c r="F4" s="16">
+        <v>1</v>
+      </c>
+      <c r="G4" s="17">
+        <v>5.2</v>
+      </c>
+      <c r="H4" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="22" customHeight="1">
+      <c r="A5" s="5"/>
+      <c r="B5" s="2">
+        <v>4</v>
+      </c>
+      <c r="C5" s="16">
+        <v>50</v>
+      </c>
+      <c r="D5" s="17">
+        <v>30</v>
+      </c>
+      <c r="E5" s="18">
+        <v>0.84000000000000008</v>
+      </c>
+      <c r="F5" s="16">
+        <v>1</v>
+      </c>
+      <c r="G5" s="17">
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H5" s="16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="22" customHeight="1">
+      <c r="A6" s="5"/>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="16">
+        <v>68</v>
+      </c>
+      <c r="D6" s="17">
+        <v>31.6</v>
+      </c>
+      <c r="E6" s="18">
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1</v>
+      </c>
+      <c r="G6" s="17">
+        <v>5.4</v>
+      </c>
+      <c r="H6" s="16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="22" customHeight="1">
+      <c r="A7" s="5"/>
+      <c r="B7" s="2">
+        <v>6</v>
+      </c>
+      <c r="C7" s="16">
+        <v>90</v>
+      </c>
+      <c r="D7" s="17">
+        <v>32.9</v>
+      </c>
+      <c r="E7" s="18">
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1</v>
+      </c>
+      <c r="G7" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="H7" s="16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="22" customHeight="1">
+      <c r="A8" s="5"/>
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+      <c r="C8" s="16">
+        <v>116</v>
+      </c>
+      <c r="D8" s="17">
+        <v>34</v>
+      </c>
+      <c r="E8" s="18">
+        <v>0.87000000000000011</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1</v>
+      </c>
+      <c r="G8" s="17">
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="H8" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="22" customHeight="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="2">
+        <v>8</v>
+      </c>
+      <c r="C9" s="16">
+        <v>146</v>
+      </c>
+      <c r="D9" s="17">
+        <v>35</v>
+      </c>
+      <c r="E9" s="18">
+        <v>0.88</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1</v>
+      </c>
+      <c r="G9" s="17">
+        <v>5.7</v>
+      </c>
+      <c r="H9" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="22" customHeight="1">
+      <c r="A10" s="5"/>
+      <c r="B10" s="2">
+        <v>9</v>
+      </c>
+      <c r="C10" s="16">
+        <v>180</v>
+      </c>
+      <c r="D10" s="17">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="E10" s="18">
+        <v>0.89</v>
+      </c>
+      <c r="F10" s="16">
+        <v>1</v>
+      </c>
+      <c r="G10" s="17">
+        <v>5.8000000000000007</v>
+      </c>
+      <c r="H10" s="16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="22" customHeight="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="2">
+        <v>10</v>
+      </c>
+      <c r="C11" s="16">
+        <v>218</v>
+      </c>
+      <c r="D11" s="17">
+        <v>36.6</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0.9</v>
+      </c>
+      <c r="F11" s="16">
+        <v>1</v>
+      </c>
+      <c r="G11" s="17">
+        <v>5.9</v>
+      </c>
+      <c r="H11" s="16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="22" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2">
+        <v>11</v>
+      </c>
+      <c r="C12" s="16">
+        <v>260</v>
+      </c>
+      <c r="D12" s="17">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="E12" s="18">
+        <v>0.91</v>
+      </c>
+      <c r="F12" s="16">
+        <v>1</v>
+      </c>
+      <c r="G12" s="17">
+        <v>6</v>
+      </c>
+      <c r="H12" s="16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="22" customHeight="1">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2">
+        <v>12</v>
+      </c>
+      <c r="C13" s="16">
+        <v>306</v>
+      </c>
+      <c r="D13" s="17">
+        <v>37.9</v>
+      </c>
+      <c r="E13" s="18">
+        <v>0.92</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
+      <c r="G13" s="17">
+        <v>6.1000000000000005</v>
+      </c>
+      <c r="H13" s="16">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="22" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="2">
+        <v>13</v>
+      </c>
+      <c r="C14" s="16">
+        <v>356</v>
+      </c>
+      <c r="D14" s="17">
+        <v>38.5</v>
+      </c>
+      <c r="E14" s="18">
+        <v>0.93</v>
+      </c>
+      <c r="F14" s="16">
+        <v>1</v>
+      </c>
+      <c r="G14" s="17">
+        <v>6.2</v>
+      </c>
+      <c r="H14" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="22" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="16">
+        <v>410</v>
+      </c>
+      <c r="D15" s="17">
+        <v>39</v>
+      </c>
+      <c r="E15" s="18">
+        <v>0.94000000000000006</v>
+      </c>
+      <c r="F15" s="16">
+        <v>1</v>
+      </c>
+      <c r="G15" s="17">
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="H15" s="16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="22" customHeight="1">
+      <c r="A16" s="5"/>
+      <c r="B16" s="2">
+        <v>15</v>
+      </c>
+      <c r="C16" s="16">
+        <v>468</v>
+      </c>
+      <c r="D16" s="17">
+        <v>39.5</v>
+      </c>
+      <c r="E16" s="18">
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="F16" s="16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="17">
+        <v>6.4</v>
+      </c>
+      <c r="H16" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="22" customHeight="1">
+      <c r="A17" s="5"/>
+      <c r="B17" s="2">
+        <v>16</v>
+      </c>
+      <c r="C17" s="16">
+        <v>530</v>
+      </c>
+      <c r="D17" s="17">
+        <v>40</v>
+      </c>
+      <c r="E17" s="18">
+        <v>0.96000000000000008</v>
+      </c>
+      <c r="F17" s="16">
+        <v>1</v>
+      </c>
+      <c r="G17" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="H17" s="16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="22" customHeight="1">
+      <c r="A18" s="5"/>
+      <c r="B18" s="2">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16">
+        <v>596</v>
+      </c>
+      <c r="D18" s="17">
+        <v>40.4</v>
+      </c>
+      <c r="E18" s="18">
+        <v>0.97000000000000008</v>
+      </c>
+      <c r="F18" s="16">
+        <v>1</v>
+      </c>
+      <c r="G18" s="17">
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="H18" s="16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="22" customHeight="1">
+      <c r="A19" s="5"/>
+      <c r="B19" s="2">
+        <v>18</v>
+      </c>
+      <c r="C19" s="16">
+        <v>666</v>
+      </c>
+      <c r="D19" s="17">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E19" s="18">
+        <v>0.98</v>
+      </c>
+      <c r="F19" s="16">
+        <v>1</v>
+      </c>
+      <c r="G19" s="17">
+        <v>6.7</v>
+      </c>
+      <c r="H19" s="16">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="22" customHeight="1">
+      <c r="A20" s="5"/>
+      <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="C20" s="16">
+        <v>740</v>
+      </c>
+      <c r="D20" s="17">
+        <v>41.2</v>
+      </c>
+      <c r="E20" s="18">
+        <v>0.99</v>
+      </c>
+      <c r="F20" s="16">
+        <v>1</v>
+      </c>
+      <c r="G20" s="17">
+        <v>6.8000000000000007</v>
+      </c>
+      <c r="H20" s="16">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="22" customHeight="1">
+      <c r="A21" s="5"/>
+      <c r="B21" s="2">
+        <v>20</v>
+      </c>
+      <c r="C21" s="16">
+        <v>818</v>
+      </c>
+      <c r="D21" s="17">
+        <v>41.6</v>
+      </c>
+      <c r="E21" s="18">
+        <v>1</v>
+      </c>
+      <c r="F21" s="16">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17">
+        <v>6.9</v>
+      </c>
+      <c r="H21" s="16">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2DE063-D8A2-496C-84E7-D026523D135F}">
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -557,327 +1114,327 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9">
         <v>400</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="9">
         <v>30</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="9">
         <v>0.24</v>
       </c>
-      <c r="F2" s="8">
-        <v>1</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="F2" s="9">
+        <v>1</v>
+      </c>
+      <c r="G2" s="9">
         <v>4</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="9">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="9">
         <v>800</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="9">
         <v>60</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="9">
         <v>0.48</v>
       </c>
-      <c r="F3" s="8">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8">
+      <c r="F3" s="9">
+        <v>1</v>
+      </c>
+      <c r="G3" s="9">
         <v>5</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="9">
         <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="9">
         <v>1200</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="9">
         <v>90</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="9">
         <v>0.72</v>
       </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8">
+      <c r="F4" s="9">
+        <v>1</v>
+      </c>
+      <c r="G4" s="9">
         <v>6</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9">
         <v>4</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="9">
         <v>1600</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="9">
         <v>120</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="9">
         <v>0.96</v>
       </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="F5" s="9">
+        <v>1</v>
+      </c>
+      <c r="G5" s="9">
         <v>7</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="9">
         <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11">
         <v>5</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="11">
         <v>2000</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="11">
         <v>150</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="11">
         <v>1.2</v>
       </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>8</v>
-      </c>
-      <c r="H6" s="10">
+      <c r="F6" s="11">
+        <v>1</v>
+      </c>
+      <c r="G6" s="11">
+        <v>8</v>
+      </c>
+      <c r="H6" s="11">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="e" cm="1">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="e" cm="1">
         <f t="array" ref="C7">x*400</f>
         <v>#NAME?</v>
       </c>
-      <c r="D7" s="8" t="e" cm="1">
+      <c r="D7" s="9" t="e" cm="1">
         <f t="array" ref="D7">x*30</f>
         <v>#NAME?</v>
       </c>
-      <c r="E7" s="8" t="e" cm="1">
+      <c r="E7" s="9" t="e" cm="1">
         <f t="array" ref="E7">0.8*(x*0.3)</f>
         <v>#NAME?</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="e" cm="1">
+      <c r="F7" s="9"/>
+      <c r="G7" s="9" t="e" cm="1">
         <f t="array" ref="G7">3+x*1</f>
         <v>#NAME?</v>
       </c>
-      <c r="H7" s="8" t="e" cm="1">
+      <c r="H7" s="9" t="e" cm="1">
         <f t="array" ref="H7">x*100</f>
         <v>#NAME?</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:8" ht="22" customHeight="1">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:8" ht="22" customHeight="1">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:8" ht="22" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:8" ht="22" customHeight="1">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8" ht="22" customHeight="1">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8" ht="22" customHeight="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" ht="22" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
     </row>
     <row r="21" spans="1:8" ht="22" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
     </row>
     <row r="22" spans="1:8" ht="28" customHeight="1">
-      <c r="A22" s="13"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -885,7 +1442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{497B63CF-FA81-4BB0-925E-C1315D62E26D}">
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -901,534 +1458,534 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9">
         <v>72</v>
       </c>
-      <c r="D2" s="8">
-        <v>8</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="D2" s="9">
+        <v>8</v>
+      </c>
+      <c r="E2" s="9">
         <v>0.5</v>
       </c>
-      <c r="F2" s="8">
-        <v>8</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="F2" s="9">
+        <v>8</v>
+      </c>
+      <c r="G2" s="9">
         <v>3</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="9">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="9">
         <v>74</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="9">
         <v>11</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="9">
         <v>0.5</v>
       </c>
-      <c r="F3" s="8">
-        <v>8</v>
-      </c>
-      <c r="G3" s="8">
+      <c r="F3" s="9">
+        <v>8</v>
+      </c>
+      <c r="G3" s="9">
         <v>3.2</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="9">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="9">
         <v>76</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="9">
         <v>14</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="9">
         <v>0.51</v>
       </c>
-      <c r="F4" s="8">
-        <v>8</v>
-      </c>
-      <c r="G4" s="8">
+      <c r="F4" s="9">
+        <v>8</v>
+      </c>
+      <c r="G4" s="9">
         <v>3.4</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="9">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9">
         <v>4</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="9">
         <v>78</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="9">
         <v>17</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="9">
         <v>0.52</v>
       </c>
-      <c r="F5" s="8">
-        <v>8</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="F5" s="9">
+        <v>8</v>
+      </c>
+      <c r="G5" s="9">
         <v>3.6</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="9">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9">
         <v>5</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <v>80</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <v>20</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <v>0.53</v>
       </c>
-      <c r="F6" s="8">
-        <v>8</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="F6" s="9">
+        <v>8</v>
+      </c>
+      <c r="G6" s="9">
         <v>3.8</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9">
         <v>6</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <v>82</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="9">
         <v>23</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>0.54</v>
       </c>
-      <c r="F7" s="8">
-        <v>8</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="F7" s="9">
+        <v>8</v>
+      </c>
+      <c r="G7" s="9">
         <v>4</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9">
         <v>7</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="9">
         <v>84</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="9">
         <v>26</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F8" s="8">
-        <v>8</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="F8" s="9">
+        <v>8</v>
+      </c>
+      <c r="G8" s="9">
         <v>4.2</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="9">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8">
-        <v>8</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9">
         <v>86</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <v>29</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <v>0.56000000000000005</v>
       </c>
-      <c r="F9" s="8">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="F9" s="9">
+        <v>8</v>
+      </c>
+      <c r="G9" s="9">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="9">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9">
         <v>9</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="9">
         <v>88</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <v>32</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="9">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F10" s="8">
-        <v>8</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="F10" s="9">
+        <v>8</v>
+      </c>
+      <c r="G10" s="9">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9">
         <v>10</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="9">
         <v>90</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="9">
         <v>35</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="9">
         <v>0.6</v>
       </c>
-      <c r="F11" s="8">
-        <v>8</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="F11" s="9">
+        <v>8</v>
+      </c>
+      <c r="G11" s="9">
         <v>4.8</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="9">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9">
         <v>11</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="9">
         <v>92</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="9">
         <v>38</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="9">
         <v>0.62</v>
       </c>
-      <c r="F12" s="8">
-        <v>8</v>
-      </c>
-      <c r="G12" s="8">
+      <c r="F12" s="9">
+        <v>8</v>
+      </c>
+      <c r="G12" s="9">
         <v>5</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="9">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9">
         <v>12</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="9">
         <v>94</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="9">
         <v>41</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="9">
         <v>0.64</v>
       </c>
-      <c r="F13" s="8">
-        <v>8</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="F13" s="9">
+        <v>8</v>
+      </c>
+      <c r="G13" s="9">
         <v>5.2</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="9">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9">
         <v>13</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <v>96</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <v>44</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <v>0.67</v>
       </c>
-      <c r="F14" s="8">
-        <v>8</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="F14" s="9">
+        <v>8</v>
+      </c>
+      <c r="G14" s="9">
         <v>5.4</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9">
         <v>14</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="9">
         <v>98</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <v>47</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <v>0.7</v>
       </c>
-      <c r="F15" s="8">
-        <v>8</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="F15" s="9">
+        <v>8</v>
+      </c>
+      <c r="G15" s="9">
         <v>5.6</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9">
         <v>15</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="9">
         <v>100</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="9">
         <v>50</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="9">
         <v>0.73</v>
       </c>
-      <c r="F16" s="8">
-        <v>8</v>
-      </c>
-      <c r="G16" s="8">
+      <c r="F16" s="9">
+        <v>8</v>
+      </c>
+      <c r="G16" s="9">
         <v>5.8</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="9">
         <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9">
         <v>16</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="9">
         <v>102</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="9">
         <v>53</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="9">
         <v>0.76</v>
       </c>
-      <c r="F17" s="8">
-        <v>8</v>
-      </c>
-      <c r="G17" s="8">
+      <c r="F17" s="9">
+        <v>8</v>
+      </c>
+      <c r="G17" s="9">
         <v>6</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="9">
         <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9">
         <v>17</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <v>104</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
         <v>56</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9">
         <v>0.79</v>
       </c>
-      <c r="F18" s="8">
-        <v>8</v>
-      </c>
-      <c r="G18" s="8">
+      <c r="F18" s="9">
+        <v>8</v>
+      </c>
+      <c r="G18" s="9">
         <v>6.2</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9">
         <v>18</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <v>106</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="9">
         <v>59</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9">
         <v>0.82</v>
       </c>
-      <c r="F19" s="8">
-        <v>8</v>
-      </c>
-      <c r="G19" s="8">
+      <c r="F19" s="9">
+        <v>8</v>
+      </c>
+      <c r="G19" s="9">
         <v>6.4</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="9">
         <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9">
         <v>19</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="9">
         <v>108</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="9">
         <v>62</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="9">
         <v>0.86</v>
       </c>
-      <c r="F20" s="8">
-        <v>8</v>
-      </c>
-      <c r="G20" s="8">
+      <c r="F20" s="9">
+        <v>8</v>
+      </c>
+      <c r="G20" s="9">
         <v>6.6</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="9">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9">
         <v>20</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="9">
         <v>110</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="9">
         <v>65</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="9">
         <v>0.9</v>
       </c>
-      <c r="F21" s="8">
-        <v>8</v>
-      </c>
-      <c r="G21" s="8">
+      <c r="F21" s="9">
+        <v>8</v>
+      </c>
+      <c r="G21" s="9">
         <v>6.8</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="9">
         <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="28" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="e" cm="1">
+      <c r="A22" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9" t="e" cm="1">
         <f t="array" ref="C22">x*2 + 70</f>
         <v>#NAME?</v>
       </c>
-      <c r="D22" s="8" t="e" cm="1">
+      <c r="D22" s="9" t="e" cm="1">
         <f t="array" ref="D22">x*3+5</f>
         <v>#NAME?</v>
       </c>
-      <c r="E22" s="8" t="e" cm="1">
+      <c r="E22" s="9" t="e" cm="1">
         <f t="array" ref="E22">0.5 + x*x*0.001</f>
         <v>#NAME?</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8" t="e" cm="1">
+      <c r="F22" s="9"/>
+      <c r="G22" s="9" t="e" cm="1">
         <f t="array" ref="G22">2.8+x*0.2</f>
         <v>#NAME?</v>
       </c>
-      <c r="H22" s="8" t="e" cm="1">
+      <c r="H22" s="9" t="e" cm="1">
         <f t="array" ref="H22">x*3 + 7</f>
         <v>#NAME?</v>
       </c>
@@ -1439,7 +1996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -1481,482 +2038,482 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
-      <c r="A2" s="4"/>
+      <c r="A2" s="5"/>
       <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="16">
         <v>20</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="17">
         <v>20</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="18">
         <v>0.81</v>
       </c>
-      <c r="F2" s="15">
-        <v>1</v>
-      </c>
-      <c r="G2" s="16">
+      <c r="F2" s="16">
+        <v>1</v>
+      </c>
+      <c r="G2" s="17">
         <v>5</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="16">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1">
-      <c r="A3" s="4"/>
+      <c r="A3" s="5"/>
       <c r="B3" s="2">
         <v>2</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="16">
         <v>26</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="17">
         <v>25</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="18">
         <v>0.82000000000000006</v>
       </c>
-      <c r="F3" s="15">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
+      <c r="F3" s="16">
+        <v>1</v>
+      </c>
+      <c r="G3" s="17">
         <v>5.1000000000000005</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="16">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22" customHeight="1">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
       <c r="B4" s="2">
         <v>3</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="16">
         <v>36</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="17">
         <v>27.9</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="18">
         <v>0.83000000000000007</v>
       </c>
-      <c r="F4" s="15">
-        <v>1</v>
-      </c>
-      <c r="G4" s="16">
+      <c r="F4" s="16">
+        <v>1</v>
+      </c>
+      <c r="G4" s="17">
         <v>5.2</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="16">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="2">
         <v>4</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <v>50</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>30</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <v>0.84000000000000008</v>
       </c>
-      <c r="F5" s="15">
-        <v>1</v>
-      </c>
-      <c r="G5" s="16">
+      <c r="F5" s="16">
+        <v>1</v>
+      </c>
+      <c r="G5" s="17">
         <v>5.3000000000000007</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="16">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1">
-      <c r="A6" s="4"/>
+      <c r="A6" s="5"/>
       <c r="B6" s="2">
         <v>5</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <v>68</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="17">
         <v>31.6</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <v>0.85000000000000009</v>
       </c>
-      <c r="F6" s="15">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16">
+      <c r="F6" s="16">
+        <v>1</v>
+      </c>
+      <c r="G6" s="17">
         <v>5.4</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="16">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="2">
         <v>6</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="16">
         <v>90</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="17">
         <v>32.9</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <v>0.8600000000000001</v>
       </c>
-      <c r="F7" s="15">
-        <v>1</v>
-      </c>
-      <c r="G7" s="16">
+      <c r="F7" s="16">
+        <v>1</v>
+      </c>
+      <c r="G7" s="17">
         <v>5.5</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="16">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1">
-      <c r="A8" s="4"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="2">
         <v>7</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="16">
         <v>116</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="17">
         <v>34</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <v>0.87000000000000011</v>
       </c>
-      <c r="F8" s="15">
-        <v>1</v>
-      </c>
-      <c r="G8" s="16">
+      <c r="F8" s="16">
+        <v>1</v>
+      </c>
+      <c r="G8" s="17">
         <v>5.6000000000000005</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="16">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="2">
         <v>8</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="16">
         <v>146</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="17">
         <v>35</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="18">
         <v>0.88</v>
       </c>
-      <c r="F9" s="15">
-        <v>1</v>
-      </c>
-      <c r="G9" s="16">
+      <c r="F9" s="16">
+        <v>1</v>
+      </c>
+      <c r="G9" s="17">
         <v>5.7</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="16">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22" customHeight="1">
-      <c r="A10" s="4"/>
+      <c r="A10" s="5"/>
       <c r="B10" s="2">
         <v>9</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="16">
         <v>180</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="17">
         <v>35.799999999999997</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="18">
         <v>0.89</v>
       </c>
-      <c r="F10" s="15">
-        <v>1</v>
-      </c>
-      <c r="G10" s="16">
+      <c r="F10" s="16">
+        <v>1</v>
+      </c>
+      <c r="G10" s="17">
         <v>5.8000000000000007</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="16">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22" customHeight="1">
-      <c r="A11" s="4"/>
+      <c r="A11" s="5"/>
       <c r="B11" s="2">
         <v>10</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="16">
         <v>218</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="17">
         <v>36.6</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="18">
         <v>0.9</v>
       </c>
-      <c r="F11" s="15">
-        <v>1</v>
-      </c>
-      <c r="G11" s="16">
+      <c r="F11" s="16">
+        <v>1</v>
+      </c>
+      <c r="G11" s="17">
         <v>5.9</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="16">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22" customHeight="1">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5"/>
       <c r="B12" s="2">
         <v>11</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="16">
         <v>260</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="17">
         <v>37.299999999999997</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="18">
         <v>0.91</v>
       </c>
-      <c r="F12" s="15">
-        <v>1</v>
-      </c>
-      <c r="G12" s="16">
+      <c r="F12" s="16">
+        <v>1</v>
+      </c>
+      <c r="G12" s="17">
         <v>6</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="16">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1">
-      <c r="A13" s="4"/>
+      <c r="A13" s="5"/>
       <c r="B13" s="2">
         <v>12</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="16">
         <v>306</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="17">
         <v>37.9</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="18">
         <v>0.92</v>
       </c>
-      <c r="F13" s="15">
-        <v>1</v>
-      </c>
-      <c r="G13" s="16">
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
+      <c r="G13" s="17">
         <v>6.1000000000000005</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="16">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22" customHeight="1">
-      <c r="A14" s="4"/>
+      <c r="A14" s="5"/>
       <c r="B14" s="2">
         <v>13</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="16">
         <v>356</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="17">
         <v>38.5</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="18">
         <v>0.93</v>
       </c>
-      <c r="F14" s="15">
-        <v>1</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F14" s="16">
+        <v>1</v>
+      </c>
+      <c r="G14" s="17">
         <v>6.2</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="16">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22" customHeight="1">
-      <c r="A15" s="4"/>
+      <c r="A15" s="5"/>
       <c r="B15" s="2">
         <v>14</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="16">
         <v>410</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="17">
         <v>39</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="18">
         <v>0.94000000000000006</v>
       </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="16">
+      <c r="F15" s="16">
+        <v>1</v>
+      </c>
+      <c r="G15" s="17">
         <v>6.3000000000000007</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="16">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
-      <c r="A16" s="4"/>
+      <c r="A16" s="5"/>
       <c r="B16" s="2">
         <v>15</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="16">
         <v>468</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <v>39.5</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="18">
         <v>0.95000000000000007</v>
       </c>
-      <c r="F16" s="15">
-        <v>1</v>
-      </c>
-      <c r="G16" s="16">
+      <c r="F16" s="16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="17">
         <v>6.4</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="16">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
-      <c r="A17" s="4"/>
+      <c r="A17" s="5"/>
       <c r="B17" s="2">
         <v>16</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <v>530</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <v>40</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="18">
         <v>0.96000000000000008</v>
       </c>
-      <c r="F17" s="15">
-        <v>1</v>
-      </c>
-      <c r="G17" s="16">
+      <c r="F17" s="16">
+        <v>1</v>
+      </c>
+      <c r="G17" s="17">
         <v>6.5</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="16">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
-      <c r="A18" s="4"/>
+      <c r="A18" s="5"/>
       <c r="B18" s="2">
         <v>17</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="16">
         <v>596</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="17">
         <v>40.4</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="18">
         <v>0.97000000000000008</v>
       </c>
-      <c r="F18" s="15">
-        <v>1</v>
-      </c>
-      <c r="G18" s="16">
+      <c r="F18" s="16">
+        <v>1</v>
+      </c>
+      <c r="G18" s="17">
         <v>6.6000000000000005</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="16">
         <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22" customHeight="1">
-      <c r="A19" s="4"/>
+      <c r="A19" s="5"/>
       <c r="B19" s="2">
         <v>18</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="16">
         <v>666</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="17">
         <v>40.799999999999997</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="18">
         <v>0.98</v>
       </c>
-      <c r="F19" s="15">
-        <v>1</v>
-      </c>
-      <c r="G19" s="16">
+      <c r="F19" s="16">
+        <v>1</v>
+      </c>
+      <c r="G19" s="17">
         <v>6.7</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="16">
         <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22" customHeight="1">
-      <c r="A20" s="4"/>
+      <c r="A20" s="5"/>
       <c r="B20" s="2">
         <v>19</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="16">
         <v>740</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="17">
         <v>41.2</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="18">
         <v>0.99</v>
       </c>
-      <c r="F20" s="15">
-        <v>1</v>
-      </c>
-      <c r="G20" s="16">
+      <c r="F20" s="16">
+        <v>1</v>
+      </c>
+      <c r="G20" s="17">
         <v>6.8000000000000007</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="16">
         <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22" customHeight="1">
-      <c r="A21" s="4"/>
+      <c r="A21" s="5"/>
       <c r="B21" s="2">
         <v>20</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="16">
         <v>818</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="17">
         <v>41.6</v>
       </c>
-      <c r="E21" s="17">
-        <v>1</v>
-      </c>
-      <c r="F21" s="15">
-        <v>1</v>
-      </c>
-      <c r="G21" s="16">
+      <c r="E21" s="18">
+        <v>1</v>
+      </c>
+      <c r="F21" s="16">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17">
         <v>6.9</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="16">
         <v>29</v>
       </c>
     </row>

--- a/GameData/GameData_Enemy.xlsx
+++ b/GameData/GameData_Enemy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ac19dd172dbe555/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7452D781-64BD-46B9-8AD0-E9162AFA9D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{A54FC7B7-0F9A-49AC-997C-278178F58BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5518842C-D2C3-41D3-82E2-B42727920717}"/>
   <bookViews>
-    <workbookView xWindow="5270" yWindow="1910" windowWidth="20360" windowHeight="13180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyInfo" sheetId="7" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -667,7 +665,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -696,7 +694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1">
+    <row r="2" spans="1:6" ht="22.05" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>22</v>
       </c>
@@ -716,7 +714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1">
+    <row r="3" spans="1:6" ht="22.05" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>26</v>
       </c>
@@ -736,7 +734,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1">
+    <row r="4" spans="1:6" ht="22.05" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>30</v>
       </c>
@@ -770,7 +768,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -800,12 +798,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1">
+    <row r="2" spans="1:6" ht="22.05" customHeight="1">
       <c r="A2" s="14">
         <v>3</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C2" s="13">
         <v>1</v>
@@ -820,7 +818,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1">
+    <row r="3" spans="1:6" ht="22.05" customHeight="1">
       <c r="A3" s="14">
         <v>5</v>
       </c>
@@ -840,7 +838,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1">
+    <row r="4" spans="1:6" ht="22.05" customHeight="1">
       <c r="A4" s="14">
         <v>15</v>
       </c>
@@ -860,7 +858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1">
+    <row r="5" spans="1:6" ht="22.05" customHeight="1">
       <c r="A5" s="14">
         <v>22</v>
       </c>
@@ -880,7 +878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1">
+    <row r="6" spans="1:6" ht="22.05" customHeight="1">
       <c r="A6" s="14">
         <v>28</v>
       </c>
@@ -900,7 +898,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1">
+    <row r="7" spans="1:6" ht="22.05" customHeight="1">
       <c r="A7" s="14">
         <v>34</v>
       </c>
@@ -920,7 +918,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1">
+    <row r="8" spans="1:6" ht="22.05" customHeight="1">
       <c r="A8" s="14">
         <v>40</v>
       </c>
@@ -940,7 +938,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1">
+    <row r="9" spans="1:6" ht="22.05" customHeight="1">
       <c r="A9" s="14">
         <v>47</v>
       </c>
@@ -960,7 +958,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1">
+    <row r="10" spans="1:6" ht="22.05" customHeight="1">
       <c r="A10" s="14">
         <v>54</v>
       </c>
@@ -980,7 +978,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1">
+    <row r="11" spans="1:6" ht="22.05" customHeight="1">
       <c r="A11" s="14">
         <v>60</v>
       </c>
@@ -1000,7 +998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1">
+    <row r="12" spans="1:6" ht="22.05" customHeight="1">
       <c r="A12" s="14">
         <v>65</v>
       </c>
@@ -1020,7 +1018,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1">
+    <row r="13" spans="1:6" ht="22.05" customHeight="1">
       <c r="A13" s="14">
         <v>71</v>
       </c>
@@ -1040,7 +1038,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1">
+    <row r="14" spans="1:6" ht="22.05" customHeight="1">
       <c r="A14" s="14">
         <v>77</v>
       </c>
@@ -1060,7 +1058,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1">
+    <row r="15" spans="1:6" ht="22.05" customHeight="1">
       <c r="A15" s="14">
         <v>84</v>
       </c>
@@ -1080,7 +1078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1">
+    <row r="16" spans="1:6" ht="22.05" customHeight="1">
       <c r="A16" s="14">
         <v>90</v>
       </c>
@@ -1100,7 +1098,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1">
+    <row r="17" spans="1:6" ht="22.05" customHeight="1">
       <c r="A17" s="14">
         <v>96</v>
       </c>
@@ -1120,7 +1118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1">
+    <row r="18" spans="1:6" ht="22.05" customHeight="1">
       <c r="A18" s="14">
         <v>100</v>
       </c>
@@ -1140,7 +1138,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1">
+    <row r="19" spans="1:6" ht="22.05" customHeight="1">
       <c r="A19" s="14">
         <v>105</v>
       </c>
@@ -1160,7 +1158,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1">
+    <row r="20" spans="1:6" ht="22.05" customHeight="1">
       <c r="A20" s="14">
         <v>110</v>
       </c>
@@ -1180,7 +1178,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1">
+    <row r="21" spans="1:6" ht="22.05" customHeight="1">
       <c r="A21" s="14">
         <v>115</v>
       </c>
@@ -1200,7 +1198,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1">
+    <row r="22" spans="1:6" ht="22.05" customHeight="1">
       <c r="A22" s="14">
         <v>118</v>
       </c>
@@ -1242,7 +1240,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1280,7 +1278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22" customHeight="1">
+    <row r="2" spans="1:8" ht="22.05" customHeight="1">
       <c r="A2" s="17"/>
       <c r="B2" s="18">
         <v>1</v>
@@ -1304,7 +1302,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22" customHeight="1">
+    <row r="3" spans="1:8" ht="22.05" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="18">
         <v>2</v>
@@ -1328,7 +1326,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22" customHeight="1">
+    <row r="4" spans="1:8" ht="22.05" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="18">
         <v>3</v>
@@ -1352,7 +1350,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22" customHeight="1">
+    <row r="5" spans="1:8" ht="22.05" customHeight="1">
       <c r="A5" s="17"/>
       <c r="B5" s="18">
         <v>4</v>
@@ -1376,7 +1374,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22" customHeight="1">
+    <row r="6" spans="1:8" ht="22.05" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <v>5</v>
@@ -1400,7 +1398,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28" customHeight="1">
+    <row r="7" spans="1:8" ht="28.05" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>8</v>
       </c>
@@ -1422,7 +1420,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22" customHeight="1">
+    <row r="8" spans="1:8" ht="22.05" customHeight="1">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1432,7 +1430,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="22" customHeight="1">
+    <row r="9" spans="1:8" ht="22.05" customHeight="1">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1442,7 +1440,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="22" customHeight="1">
+    <row r="10" spans="1:8" ht="22.05" customHeight="1">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1452,7 +1450,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="22" customHeight="1">
+    <row r="11" spans="1:8" ht="22.05" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1462,7 +1460,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="22" customHeight="1">
+    <row r="12" spans="1:8" ht="22.05" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1472,7 +1470,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="22" customHeight="1">
+    <row r="13" spans="1:8" ht="22.05" customHeight="1">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1482,7 +1480,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="22" customHeight="1">
+    <row r="14" spans="1:8" ht="22.05" customHeight="1">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1492,7 +1490,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1">
+    <row r="15" spans="1:8" ht="22.05" customHeight="1">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1502,7 +1500,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1">
+    <row r="16" spans="1:8" ht="22.05" customHeight="1">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1512,7 +1510,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
+    <row r="17" spans="1:8" ht="22.05" customHeight="1">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1522,7 +1520,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="22" customHeight="1">
+    <row r="18" spans="1:8" ht="22.05" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1532,7 +1530,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="22" customHeight="1">
+    <row r="19" spans="1:8" ht="22.05" customHeight="1">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1542,7 +1540,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="22" customHeight="1">
+    <row r="20" spans="1:8" ht="22.05" customHeight="1">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1552,7 +1550,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="22" customHeight="1">
+    <row r="21" spans="1:8" ht="22.05" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1562,7 +1560,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" ht="28" customHeight="1">
+    <row r="22" spans="1:8" ht="28.05" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1581,7 +1579,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1619,7 +1617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22" customHeight="1">
+    <row r="2" spans="1:8" ht="22.05" customHeight="1">
       <c r="A2" s="17"/>
       <c r="B2" s="18">
         <v>1</v>
@@ -1643,7 +1641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22" customHeight="1">
+    <row r="3" spans="1:8" ht="22.05" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="18">
         <v>2</v>
@@ -1667,7 +1665,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22" customHeight="1">
+    <row r="4" spans="1:8" ht="22.05" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="18">
         <v>3</v>
@@ -1691,7 +1689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22" customHeight="1">
+    <row r="5" spans="1:8" ht="22.05" customHeight="1">
       <c r="A5" s="17"/>
       <c r="B5" s="18">
         <v>4</v>
@@ -1715,7 +1713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22" customHeight="1">
+    <row r="6" spans="1:8" ht="22.05" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <v>5</v>
@@ -1739,7 +1737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22" customHeight="1">
+    <row r="7" spans="1:8" ht="22.05" customHeight="1">
       <c r="A7" s="17"/>
       <c r="B7" s="18">
         <v>6</v>
@@ -1763,7 +1761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22" customHeight="1">
+    <row r="8" spans="1:8" ht="22.05" customHeight="1">
       <c r="A8" s="17"/>
       <c r="B8" s="18">
         <v>7</v>
@@ -1787,7 +1785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22" customHeight="1">
+    <row r="9" spans="1:8" ht="22.05" customHeight="1">
       <c r="A9" s="17"/>
       <c r="B9" s="18">
         <v>8</v>
@@ -1811,7 +1809,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22" customHeight="1">
+    <row r="10" spans="1:8" ht="22.05" customHeight="1">
       <c r="A10" s="17"/>
       <c r="B10" s="18">
         <v>9</v>
@@ -1835,7 +1833,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22" customHeight="1">
+    <row r="11" spans="1:8" ht="22.05" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="18">
         <v>10</v>
@@ -1859,7 +1857,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22" customHeight="1">
+    <row r="12" spans="1:8" ht="22.05" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="18">
         <v>11</v>
@@ -1883,7 +1881,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="22" customHeight="1">
+    <row r="13" spans="1:8" ht="22.05" customHeight="1">
       <c r="A13" s="17"/>
       <c r="B13" s="18">
         <v>12</v>
@@ -1907,7 +1905,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="22" customHeight="1">
+    <row r="14" spans="1:8" ht="22.05" customHeight="1">
       <c r="A14" s="17"/>
       <c r="B14" s="18">
         <v>13</v>
@@ -1931,7 +1929,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1">
+    <row r="15" spans="1:8" ht="22.05" customHeight="1">
       <c r="A15" s="17"/>
       <c r="B15" s="18">
         <v>14</v>
@@ -1955,7 +1953,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1">
+    <row r="16" spans="1:8" ht="22.05" customHeight="1">
       <c r="A16" s="17"/>
       <c r="B16" s="18">
         <v>15</v>
@@ -1979,7 +1977,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
+    <row r="17" spans="1:8" ht="22.05" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="18">
         <v>16</v>
@@ -2003,7 +2001,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="22" customHeight="1">
+    <row r="18" spans="1:8" ht="22.05" customHeight="1">
       <c r="A18" s="17"/>
       <c r="B18" s="18">
         <v>17</v>
@@ -2027,7 +2025,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="22" customHeight="1">
+    <row r="19" spans="1:8" ht="22.05" customHeight="1">
       <c r="A19" s="17"/>
       <c r="B19" s="18">
         <v>18</v>
@@ -2051,7 +2049,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="22" customHeight="1">
+    <row r="20" spans="1:8" ht="22.05" customHeight="1">
       <c r="A20" s="17"/>
       <c r="B20" s="18">
         <v>19</v>
@@ -2075,7 +2073,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="22" customHeight="1">
+    <row r="21" spans="1:8" ht="22.05" customHeight="1">
       <c r="A21" s="17"/>
       <c r="B21" s="18">
         <v>20</v>
@@ -2099,7 +2097,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28" customHeight="1">
+    <row r="22" spans="1:8" ht="28.05" customHeight="1">
       <c r="A22" s="19" t="s">
         <v>8</v>
       </c>
@@ -2130,7 +2128,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -2168,7 +2166,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22" customHeight="1">
+    <row r="2" spans="1:8" ht="22.05" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="2">
         <v>1</v>
@@ -2192,7 +2190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22" customHeight="1">
+    <row r="3" spans="1:8" ht="22.05" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2">
         <v>2</v>
@@ -2216,7 +2214,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22" customHeight="1">
+    <row r="4" spans="1:8" ht="22.05" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="2">
         <v>3</v>
@@ -2240,7 +2238,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22" customHeight="1">
+    <row r="5" spans="1:8" ht="22.05" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="2">
         <v>4</v>
@@ -2264,7 +2262,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22" customHeight="1">
+    <row r="6" spans="1:8" ht="22.05" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="2">
         <v>5</v>
@@ -2288,7 +2286,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22" customHeight="1">
+    <row r="7" spans="1:8" ht="22.05" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="2">
         <v>6</v>
@@ -2312,7 +2310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22" customHeight="1">
+    <row r="8" spans="1:8" ht="22.05" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="2">
         <v>7</v>
@@ -2336,7 +2334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22" customHeight="1">
+    <row r="9" spans="1:8" ht="22.05" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="2">
         <v>8</v>
@@ -2360,7 +2358,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22" customHeight="1">
+    <row r="10" spans="1:8" ht="22.05" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="2">
         <v>9</v>
@@ -2384,7 +2382,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22" customHeight="1">
+    <row r="11" spans="1:8" ht="22.05" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="2">
         <v>10</v>
@@ -2408,7 +2406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22" customHeight="1">
+    <row r="12" spans="1:8" ht="22.05" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="2">
         <v>11</v>
@@ -2432,7 +2430,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="22" customHeight="1">
+    <row r="13" spans="1:8" ht="22.05" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="2">
         <v>12</v>
@@ -2456,7 +2454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="22" customHeight="1">
+    <row r="14" spans="1:8" ht="22.05" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="2">
         <v>13</v>
@@ -2480,7 +2478,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1">
+    <row r="15" spans="1:8" ht="22.05" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="2">
         <v>14</v>
@@ -2504,7 +2502,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1">
+    <row r="16" spans="1:8" ht="22.05" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="2">
         <v>15</v>
@@ -2528,7 +2526,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
+    <row r="17" spans="1:8" ht="22.05" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="2">
         <v>16</v>
@@ -2552,7 +2550,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="22" customHeight="1">
+    <row r="18" spans="1:8" ht="22.05" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="2">
         <v>17</v>
@@ -2576,7 +2574,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="22" customHeight="1">
+    <row r="19" spans="1:8" ht="22.05" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" s="2">
         <v>18</v>
@@ -2600,7 +2598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="22" customHeight="1">
+    <row r="20" spans="1:8" ht="22.05" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="2">
         <v>19</v>
@@ -2624,7 +2622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="22" customHeight="1">
+    <row r="21" spans="1:8" ht="22.05" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="2">
         <v>20</v>
@@ -2648,7 +2646,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28" customHeight="1">
+    <row r="22" spans="1:8" ht="28.05" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>

--- a/GameData/GameData_Enemy.xlsx
+++ b/GameData/GameData_Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ac19dd172dbe555/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{A54FC7B7-0F9A-49AC-997C-278178F58BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5518842C-D2C3-41D3-82E2-B42727920717}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{2B3B6870-6ABC-4D00-B703-3597A251FC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75077F40-97A0-400A-A572-5A301D2A9233}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyInfo" sheetId="7" r:id="rId1"/>
@@ -92,18 +92,12 @@
     <t>스켈레톤</t>
   </si>
   <si>
-    <t>x*x*2 + 18</t>
-  </si>
-  <si>
     <t>LOG(x,2)*5+20</t>
   </si>
   <si>
     <t>0.8 + x*0.01</t>
   </si>
   <si>
-    <t>4.9+x*0.1</t>
-  </si>
-  <si>
     <t>x+9</t>
   </si>
   <si>
@@ -146,9 +140,6 @@
     <t>Ranged</t>
   </si>
   <si>
-    <t>Assets/Prefabs/Enemies/Goblin_Mage.prefab</t>
-  </si>
-  <si>
     <t>boss</t>
   </si>
   <si>
@@ -182,25 +173,40 @@
     <t>0.8*(x*0.3)</t>
   </si>
   <si>
-    <t>3+x</t>
-  </si>
-  <si>
     <t>x*100</t>
   </si>
   <si>
-    <t>x*2+70</t>
-  </si>
-  <si>
     <t>x*3+5</t>
   </si>
   <si>
     <t>0.5+x*x*0.001</t>
   </si>
   <si>
-    <t>2.8+x*0.2</t>
-  </si>
-  <si>
     <t>x*3+7</t>
+  </si>
+  <si>
+    <t>x*x*2+10</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>x*x*3 + 18</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/Enemies/Goblinmage.prefab</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9+x*0.1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8+x*0.2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+x</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -676,39 +682,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>19</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>25</v>
       </c>
       <c r="F2" s="13">
         <v>20</v>
@@ -716,19 +722,19 @@
     </row>
     <row r="3" spans="1:6" ht="22.05" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F3" s="13">
         <v>20</v>
@@ -736,19 +742,19 @@
     </row>
     <row r="4" spans="1:6" ht="22.05" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F4" s="13">
         <v>5</v>
@@ -780,22 +786,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1">
@@ -803,7 +809,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="13">
         <v>1</v>
@@ -823,7 +829,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="13">
         <v>1</v>
@@ -843,7 +849,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="13">
         <v>2</v>
@@ -863,7 +869,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="13">
         <v>1</v>
@@ -883,7 +889,7 @@
         <v>28</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="13">
         <v>3</v>
@@ -903,7 +909,7 @@
         <v>34</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="13">
         <v>2</v>
@@ -923,7 +929,7 @@
         <v>40</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="13">
         <v>4</v>
@@ -943,7 +949,7 @@
         <v>47</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="13">
         <v>3</v>
@@ -963,7 +969,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="13">
         <v>5</v>
@@ -983,7 +989,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" s="13">
         <v>1</v>
@@ -1003,7 +1009,7 @@
         <v>65</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="13">
         <v>6</v>
@@ -1023,7 +1029,7 @@
         <v>71</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" s="13">
         <v>4</v>
@@ -1043,7 +1049,7 @@
         <v>77</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C14" s="13">
         <v>7</v>
@@ -1063,7 +1069,7 @@
         <v>84</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" s="13">
         <v>5</v>
@@ -1083,7 +1089,7 @@
         <v>90</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C16" s="13">
         <v>8</v>
@@ -1103,7 +1109,7 @@
         <v>96</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C17" s="13">
         <v>2</v>
@@ -1123,7 +1129,7 @@
         <v>100</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" s="13">
         <v>9</v>
@@ -1143,7 +1149,7 @@
         <v>105</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="13">
         <v>6</v>
@@ -1163,7 +1169,7 @@
         <v>110</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C20" s="13">
         <v>10</v>
@@ -1183,7 +1189,7 @@
         <v>115</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" s="13">
         <v>7</v>
@@ -1203,7 +1209,7 @@
         <v>118</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C22" s="13">
         <v>3</v>
@@ -1296,7 +1302,8 @@
         <v>1</v>
       </c>
       <c r="G2" s="22">
-        <v>4</v>
+        <f>1+B2</f>
+        <v>2</v>
       </c>
       <c r="H2" s="21">
         <v>100</v>
@@ -1320,7 +1327,8 @@
         <v>1</v>
       </c>
       <c r="G3" s="22">
-        <v>5</v>
+        <f t="shared" ref="G3:G6" si="0">1+B3</f>
+        <v>3</v>
       </c>
       <c r="H3" s="21">
         <v>200</v>
@@ -1344,7 +1352,8 @@
         <v>1</v>
       </c>
       <c r="G4" s="22">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="H4" s="21">
         <v>300</v>
@@ -1368,7 +1377,8 @@
         <v>1</v>
       </c>
       <c r="G5" s="22">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="H5" s="21">
         <v>400</v>
@@ -1392,7 +1402,8 @@
         <v>1</v>
       </c>
       <c r="G6" s="22">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="H6" s="21">
         <v>500</v>
@@ -1404,20 +1415,20 @@
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20" t="s" cm="1">
+        <v>35</v>
+      </c>
+      <c r="D7" s="20" t="s" cm="1">
+        <v>36</v>
+      </c>
+      <c r="E7" s="20" t="s" cm="1">
+        <v>37</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="20" t="s" cm="1">
         <v>38</v>
-      </c>
-      <c r="D7" s="20" t="s" cm="1">
-        <v>39</v>
-      </c>
-      <c r="E7" s="20" t="s" cm="1">
-        <v>40</v>
-      </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20" t="s" cm="1">
-        <v>41</v>
-      </c>
-      <c r="H7" s="20" t="s" cm="1">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.05" customHeight="1">
@@ -1623,7 +1634,8 @@
         <v>1</v>
       </c>
       <c r="C2" s="21">
-        <v>72</v>
+        <f>10+2*B2*B2</f>
+        <v>12</v>
       </c>
       <c r="D2" s="22">
         <v>8</v>
@@ -1635,7 +1647,8 @@
         <v>8</v>
       </c>
       <c r="G2" s="22">
-        <v>3</v>
+        <f>0.8+B2*0.2</f>
+        <v>1</v>
       </c>
       <c r="H2" s="21">
         <v>10</v>
@@ -1647,7 +1660,8 @@
         <v>2</v>
       </c>
       <c r="C3" s="21">
-        <v>74</v>
+        <f t="shared" ref="C3:C21" si="0">10+2*B3*B3</f>
+        <v>18</v>
       </c>
       <c r="D3" s="22">
         <v>11</v>
@@ -1659,7 +1673,8 @@
         <v>8</v>
       </c>
       <c r="G3" s="22">
-        <v>3.2</v>
+        <f t="shared" ref="G3:G21" si="1">0.8+B3*0.2</f>
+        <v>1.2000000000000002</v>
       </c>
       <c r="H3" s="21">
         <v>13</v>
@@ -1671,7 +1686,8 @@
         <v>3</v>
       </c>
       <c r="C4" s="21">
-        <v>76</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="D4" s="22">
         <v>14</v>
@@ -1683,7 +1699,8 @@
         <v>8</v>
       </c>
       <c r="G4" s="22">
-        <v>3.4</v>
+        <f t="shared" si="1"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="H4" s="21">
         <v>16</v>
@@ -1695,7 +1712,8 @@
         <v>4</v>
       </c>
       <c r="C5" s="21">
-        <v>78</v>
+        <f t="shared" si="0"/>
+        <v>42</v>
       </c>
       <c r="D5" s="22">
         <v>17</v>
@@ -1707,7 +1725,8 @@
         <v>8</v>
       </c>
       <c r="G5" s="22">
-        <v>3.6</v>
+        <f t="shared" si="1"/>
+        <v>1.6</v>
       </c>
       <c r="H5" s="21">
         <v>19</v>
@@ -1719,7 +1738,8 @@
         <v>5</v>
       </c>
       <c r="C6" s="21">
-        <v>80</v>
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="D6" s="22">
         <v>20</v>
@@ -1731,7 +1751,8 @@
         <v>8</v>
       </c>
       <c r="G6" s="22">
-        <v>3.8</v>
+        <f t="shared" si="1"/>
+        <v>1.8</v>
       </c>
       <c r="H6" s="21">
         <v>22</v>
@@ -1743,6 +1764,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="21">
+        <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="D7" s="22">
@@ -1755,7 +1777,8 @@
         <v>8</v>
       </c>
       <c r="G7" s="22">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H7" s="21">
         <v>25</v>
@@ -1767,7 +1790,8 @@
         <v>7</v>
       </c>
       <c r="C8" s="21">
-        <v>84</v>
+        <f t="shared" si="0"/>
+        <v>108</v>
       </c>
       <c r="D8" s="22">
         <v>26</v>
@@ -1779,7 +1803,8 @@
         <v>8</v>
       </c>
       <c r="G8" s="22">
-        <v>4.2</v>
+        <f t="shared" si="1"/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H8" s="21">
         <v>28</v>
@@ -1791,7 +1816,8 @@
         <v>8</v>
       </c>
       <c r="C9" s="21">
-        <v>86</v>
+        <f t="shared" si="0"/>
+        <v>138</v>
       </c>
       <c r="D9" s="22">
         <v>29</v>
@@ -1803,7 +1829,8 @@
         <v>8</v>
       </c>
       <c r="G9" s="22">
-        <v>4.4000000000000004</v>
+        <f t="shared" si="1"/>
+        <v>2.4000000000000004</v>
       </c>
       <c r="H9" s="21">
         <v>31</v>
@@ -1815,7 +1842,8 @@
         <v>9</v>
       </c>
       <c r="C10" s="21">
-        <v>88</v>
+        <f t="shared" si="0"/>
+        <v>172</v>
       </c>
       <c r="D10" s="22">
         <v>32</v>
@@ -1827,7 +1855,8 @@
         <v>8</v>
       </c>
       <c r="G10" s="22">
-        <v>4.5999999999999996</v>
+        <f t="shared" si="1"/>
+        <v>2.6</v>
       </c>
       <c r="H10" s="21">
         <v>34</v>
@@ -1839,7 +1868,8 @@
         <v>10</v>
       </c>
       <c r="C11" s="21">
-        <v>90</v>
+        <f t="shared" si="0"/>
+        <v>210</v>
       </c>
       <c r="D11" s="22">
         <v>35</v>
@@ -1851,7 +1881,8 @@
         <v>8</v>
       </c>
       <c r="G11" s="22">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>2.8</v>
       </c>
       <c r="H11" s="21">
         <v>37</v>
@@ -1863,7 +1894,8 @@
         <v>11</v>
       </c>
       <c r="C12" s="21">
-        <v>92</v>
+        <f t="shared" si="0"/>
+        <v>252</v>
       </c>
       <c r="D12" s="22">
         <v>38</v>
@@ -1875,7 +1907,8 @@
         <v>8</v>
       </c>
       <c r="G12" s="22">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H12" s="21">
         <v>40</v>
@@ -1887,7 +1920,8 @@
         <v>12</v>
       </c>
       <c r="C13" s="21">
-        <v>94</v>
+        <f t="shared" si="0"/>
+        <v>298</v>
       </c>
       <c r="D13" s="22">
         <v>41</v>
@@ -1899,7 +1933,8 @@
         <v>8</v>
       </c>
       <c r="G13" s="22">
-        <v>5.2</v>
+        <f t="shared" si="1"/>
+        <v>3.2</v>
       </c>
       <c r="H13" s="21">
         <v>43</v>
@@ -1911,7 +1946,8 @@
         <v>13</v>
       </c>
       <c r="C14" s="21">
-        <v>96</v>
+        <f t="shared" si="0"/>
+        <v>348</v>
       </c>
       <c r="D14" s="22">
         <v>44</v>
@@ -1923,7 +1959,8 @@
         <v>8</v>
       </c>
       <c r="G14" s="22">
-        <v>5.4</v>
+        <f t="shared" si="1"/>
+        <v>3.4000000000000004</v>
       </c>
       <c r="H14" s="21">
         <v>46</v>
@@ -1935,7 +1972,8 @@
         <v>14</v>
       </c>
       <c r="C15" s="21">
-        <v>98</v>
+        <f t="shared" si="0"/>
+        <v>402</v>
       </c>
       <c r="D15" s="22">
         <v>47</v>
@@ -1947,7 +1985,8 @@
         <v>8</v>
       </c>
       <c r="G15" s="22">
-        <v>5.6</v>
+        <f t="shared" si="1"/>
+        <v>3.6000000000000005</v>
       </c>
       <c r="H15" s="21">
         <v>49</v>
@@ -1959,7 +1998,8 @@
         <v>15</v>
       </c>
       <c r="C16" s="21">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>460</v>
       </c>
       <c r="D16" s="22">
         <v>50</v>
@@ -1971,7 +2011,8 @@
         <v>8</v>
       </c>
       <c r="G16" s="22">
-        <v>5.8</v>
+        <f t="shared" si="1"/>
+        <v>3.8</v>
       </c>
       <c r="H16" s="21">
         <v>52</v>
@@ -1983,7 +2024,8 @@
         <v>16</v>
       </c>
       <c r="C17" s="21">
-        <v>102</v>
+        <f t="shared" si="0"/>
+        <v>522</v>
       </c>
       <c r="D17" s="22">
         <v>53</v>
@@ -1995,7 +2037,8 @@
         <v>8</v>
       </c>
       <c r="G17" s="22">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H17" s="21">
         <v>55</v>
@@ -2007,7 +2050,8 @@
         <v>17</v>
       </c>
       <c r="C18" s="21">
-        <v>104</v>
+        <f t="shared" si="0"/>
+        <v>588</v>
       </c>
       <c r="D18" s="22">
         <v>56</v>
@@ -2019,7 +2063,8 @@
         <v>8</v>
       </c>
       <c r="G18" s="22">
-        <v>6.2</v>
+        <f t="shared" si="1"/>
+        <v>4.2</v>
       </c>
       <c r="H18" s="21">
         <v>58</v>
@@ -2031,7 +2076,8 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <v>106</v>
+        <f t="shared" si="0"/>
+        <v>658</v>
       </c>
       <c r="D19" s="22">
         <v>59</v>
@@ -2043,7 +2089,8 @@
         <v>8</v>
       </c>
       <c r="G19" s="22">
-        <v>6.4</v>
+        <f t="shared" si="1"/>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H19" s="21">
         <v>61</v>
@@ -2055,7 +2102,8 @@
         <v>19</v>
       </c>
       <c r="C20" s="21">
-        <v>108</v>
+        <f t="shared" si="0"/>
+        <v>732</v>
       </c>
       <c r="D20" s="22">
         <v>62</v>
@@ -2067,7 +2115,8 @@
         <v>8</v>
       </c>
       <c r="G20" s="22">
-        <v>6.6</v>
+        <f t="shared" si="1"/>
+        <v>4.6000000000000005</v>
       </c>
       <c r="H20" s="21">
         <v>64</v>
@@ -2079,7 +2128,8 @@
         <v>20</v>
       </c>
       <c r="C21" s="21">
-        <v>110</v>
+        <f t="shared" si="0"/>
+        <v>810</v>
       </c>
       <c r="D21" s="22">
         <v>65</v>
@@ -2091,7 +2141,8 @@
         <v>8</v>
       </c>
       <c r="G21" s="22">
-        <v>6.8</v>
+        <f t="shared" si="1"/>
+        <v>4.8</v>
       </c>
       <c r="H21" s="21">
         <v>67</v>
@@ -2102,21 +2153,21 @@
         <v>8</v>
       </c>
       <c r="B22" s="20"/>
-      <c r="C22" s="20" t="s" cm="1">
-        <v>43</v>
+      <c r="C22" s="20" t="s">
+        <v>42</v>
       </c>
       <c r="D22" s="20" t="s" cm="1">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E22" s="20" t="s" cm="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F22" s="20"/>
-      <c r="G22" s="20" t="s" cm="1">
+      <c r="G22" s="20" t="s">
         <v>46</v>
       </c>
       <c r="H22" s="20" t="s" cm="1">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2172,6 +2223,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="8">
+        <f>B2*B2*3+17</f>
         <v>20</v>
       </c>
       <c r="D2" s="9">
@@ -2184,7 +2236,8 @@
         <v>1</v>
       </c>
       <c r="G2" s="9">
-        <v>5</v>
+        <f>1.9+B2*0.1</f>
+        <v>2</v>
       </c>
       <c r="H2" s="8">
         <v>10</v>
@@ -2196,7 +2249,8 @@
         <v>2</v>
       </c>
       <c r="C3" s="8">
-        <v>26</v>
+        <f t="shared" ref="C3:C21" si="0">B3*B3*3+17</f>
+        <v>29</v>
       </c>
       <c r="D3" s="9">
         <v>25</v>
@@ -2208,7 +2262,8 @@
         <v>1</v>
       </c>
       <c r="G3" s="9">
-        <v>5.1000000000000005</v>
+        <f t="shared" ref="G3:G21" si="1">1.9+B3*0.1</f>
+        <v>2.1</v>
       </c>
       <c r="H3" s="8">
         <v>11</v>
@@ -2220,7 +2275,8 @@
         <v>3</v>
       </c>
       <c r="C4" s="8">
-        <v>36</v>
+        <f t="shared" si="0"/>
+        <v>44</v>
       </c>
       <c r="D4" s="9">
         <v>27.9</v>
@@ -2232,7 +2288,8 @@
         <v>1</v>
       </c>
       <c r="G4" s="9">
-        <v>5.2</v>
+        <f t="shared" si="1"/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H4" s="8">
         <v>12</v>
@@ -2244,7 +2301,8 @@
         <v>4</v>
       </c>
       <c r="C5" s="8">
-        <v>50</v>
+        <f t="shared" si="0"/>
+        <v>65</v>
       </c>
       <c r="D5" s="9">
         <v>30</v>
@@ -2256,7 +2314,8 @@
         <v>1</v>
       </c>
       <c r="G5" s="9">
-        <v>5.3000000000000007</v>
+        <f t="shared" si="1"/>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H5" s="8">
         <v>13</v>
@@ -2268,7 +2327,8 @@
         <v>5</v>
       </c>
       <c r="C6" s="8">
-        <v>68</v>
+        <f t="shared" si="0"/>
+        <v>92</v>
       </c>
       <c r="D6" s="9">
         <v>31.6</v>
@@ -2280,7 +2340,8 @@
         <v>1</v>
       </c>
       <c r="G6" s="9">
-        <v>5.4</v>
+        <f t="shared" si="1"/>
+        <v>2.4</v>
       </c>
       <c r="H6" s="8">
         <v>14</v>
@@ -2292,7 +2353,8 @@
         <v>6</v>
       </c>
       <c r="C7" s="8">
-        <v>90</v>
+        <f t="shared" si="0"/>
+        <v>125</v>
       </c>
       <c r="D7" s="9">
         <v>32.9</v>
@@ -2304,7 +2366,8 @@
         <v>1</v>
       </c>
       <c r="G7" s="9">
-        <v>5.5</v>
+        <f t="shared" si="1"/>
+        <v>2.5</v>
       </c>
       <c r="H7" s="8">
         <v>15</v>
@@ -2316,7 +2379,8 @@
         <v>7</v>
       </c>
       <c r="C8" s="8">
-        <v>116</v>
+        <f t="shared" si="0"/>
+        <v>164</v>
       </c>
       <c r="D8" s="9">
         <v>34</v>
@@ -2328,7 +2392,8 @@
         <v>1</v>
       </c>
       <c r="G8" s="9">
-        <v>5.6000000000000005</v>
+        <f t="shared" si="1"/>
+        <v>2.6</v>
       </c>
       <c r="H8" s="8">
         <v>16</v>
@@ -2340,7 +2405,8 @@
         <v>8</v>
       </c>
       <c r="C9" s="8">
-        <v>146</v>
+        <f t="shared" si="0"/>
+        <v>209</v>
       </c>
       <c r="D9" s="9">
         <v>35</v>
@@ -2352,7 +2418,8 @@
         <v>1</v>
       </c>
       <c r="G9" s="9">
-        <v>5.7</v>
+        <f t="shared" si="1"/>
+        <v>2.7</v>
       </c>
       <c r="H9" s="8">
         <v>17</v>
@@ -2364,7 +2431,8 @@
         <v>9</v>
       </c>
       <c r="C10" s="8">
-        <v>180</v>
+        <f t="shared" si="0"/>
+        <v>260</v>
       </c>
       <c r="D10" s="9">
         <v>35.799999999999997</v>
@@ -2376,7 +2444,8 @@
         <v>1</v>
       </c>
       <c r="G10" s="9">
-        <v>5.8000000000000007</v>
+        <f t="shared" si="1"/>
+        <v>2.8</v>
       </c>
       <c r="H10" s="8">
         <v>18</v>
@@ -2388,7 +2457,8 @@
         <v>10</v>
       </c>
       <c r="C11" s="8">
-        <v>218</v>
+        <f t="shared" si="0"/>
+        <v>317</v>
       </c>
       <c r="D11" s="9">
         <v>36.6</v>
@@ -2400,7 +2470,8 @@
         <v>1</v>
       </c>
       <c r="G11" s="9">
-        <v>5.9</v>
+        <f t="shared" si="1"/>
+        <v>2.9</v>
       </c>
       <c r="H11" s="8">
         <v>19</v>
@@ -2412,7 +2483,8 @@
         <v>11</v>
       </c>
       <c r="C12" s="8">
-        <v>260</v>
+        <f t="shared" si="0"/>
+        <v>380</v>
       </c>
       <c r="D12" s="9">
         <v>37.299999999999997</v>
@@ -2424,7 +2496,8 @@
         <v>1</v>
       </c>
       <c r="G12" s="9">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H12" s="8">
         <v>20</v>
@@ -2436,7 +2509,8 @@
         <v>12</v>
       </c>
       <c r="C13" s="8">
-        <v>306</v>
+        <f t="shared" si="0"/>
+        <v>449</v>
       </c>
       <c r="D13" s="9">
         <v>37.9</v>
@@ -2448,7 +2522,8 @@
         <v>1</v>
       </c>
       <c r="G13" s="9">
-        <v>6.1000000000000005</v>
+        <f t="shared" si="1"/>
+        <v>3.1</v>
       </c>
       <c r="H13" s="8">
         <v>21</v>
@@ -2460,7 +2535,8 @@
         <v>13</v>
       </c>
       <c r="C14" s="8">
-        <v>356</v>
+        <f t="shared" si="0"/>
+        <v>524</v>
       </c>
       <c r="D14" s="9">
         <v>38.5</v>
@@ -2472,7 +2548,8 @@
         <v>1</v>
       </c>
       <c r="G14" s="9">
-        <v>6.2</v>
+        <f t="shared" si="1"/>
+        <v>3.2</v>
       </c>
       <c r="H14" s="8">
         <v>22</v>
@@ -2484,7 +2561,8 @@
         <v>14</v>
       </c>
       <c r="C15" s="8">
-        <v>410</v>
+        <f t="shared" si="0"/>
+        <v>605</v>
       </c>
       <c r="D15" s="9">
         <v>39</v>
@@ -2496,7 +2574,8 @@
         <v>1</v>
       </c>
       <c r="G15" s="9">
-        <v>6.3000000000000007</v>
+        <f t="shared" si="1"/>
+        <v>3.3</v>
       </c>
       <c r="H15" s="8">
         <v>23</v>
@@ -2508,7 +2587,8 @@
         <v>15</v>
       </c>
       <c r="C16" s="8">
-        <v>468</v>
+        <f t="shared" si="0"/>
+        <v>692</v>
       </c>
       <c r="D16" s="9">
         <v>39.5</v>
@@ -2520,7 +2600,8 @@
         <v>1</v>
       </c>
       <c r="G16" s="9">
-        <v>6.4</v>
+        <f t="shared" si="1"/>
+        <v>3.4</v>
       </c>
       <c r="H16" s="8">
         <v>24</v>
@@ -2532,7 +2613,8 @@
         <v>16</v>
       </c>
       <c r="C17" s="8">
-        <v>530</v>
+        <f t="shared" si="0"/>
+        <v>785</v>
       </c>
       <c r="D17" s="9">
         <v>40</v>
@@ -2544,7 +2626,8 @@
         <v>1</v>
       </c>
       <c r="G17" s="9">
-        <v>6.5</v>
+        <f t="shared" si="1"/>
+        <v>3.5</v>
       </c>
       <c r="H17" s="8">
         <v>25</v>
@@ -2556,7 +2639,8 @@
         <v>17</v>
       </c>
       <c r="C18" s="8">
-        <v>596</v>
+        <f t="shared" si="0"/>
+        <v>884</v>
       </c>
       <c r="D18" s="9">
         <v>40.4</v>
@@ -2568,7 +2652,8 @@
         <v>1</v>
       </c>
       <c r="G18" s="9">
-        <v>6.6000000000000005</v>
+        <f t="shared" si="1"/>
+        <v>3.6</v>
       </c>
       <c r="H18" s="8">
         <v>26</v>
@@ -2580,7 +2665,8 @@
         <v>18</v>
       </c>
       <c r="C19" s="8">
-        <v>666</v>
+        <f t="shared" si="0"/>
+        <v>989</v>
       </c>
       <c r="D19" s="9">
         <v>40.799999999999997</v>
@@ -2592,7 +2678,8 @@
         <v>1</v>
       </c>
       <c r="G19" s="9">
-        <v>6.7</v>
+        <f t="shared" si="1"/>
+        <v>3.7</v>
       </c>
       <c r="H19" s="8">
         <v>27</v>
@@ -2604,7 +2691,8 @@
         <v>19</v>
       </c>
       <c r="C20" s="8">
-        <v>740</v>
+        <f t="shared" si="0"/>
+        <v>1100</v>
       </c>
       <c r="D20" s="9">
         <v>41.2</v>
@@ -2616,7 +2704,8 @@
         <v>1</v>
       </c>
       <c r="G20" s="9">
-        <v>6.8000000000000007</v>
+        <f t="shared" si="1"/>
+        <v>3.8</v>
       </c>
       <c r="H20" s="8">
         <v>28</v>
@@ -2628,7 +2717,8 @@
         <v>20</v>
       </c>
       <c r="C21" s="8">
-        <v>818</v>
+        <f t="shared" si="0"/>
+        <v>1217</v>
       </c>
       <c r="D21" s="9">
         <v>41.6</v>
@@ -2640,7 +2730,8 @@
         <v>1</v>
       </c>
       <c r="G21" s="9">
-        <v>6.9</v>
+        <f t="shared" si="1"/>
+        <v>3.9</v>
       </c>
       <c r="H21" s="8">
         <v>29</v>
@@ -2652,20 +2743,20 @@
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/GameData/GameData_Enemy.xlsx
+++ b/GameData/GameData_Enemy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ac19dd172dbe555/문서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{2B3B6870-6ABC-4D00-B703-3597A251FC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75077F40-97A0-400A-A572-5A301D2A9233}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2663FC7A-66E0-4575-896B-C6601934EC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3250" yWindow="3560" windowWidth="20360" windowHeight="13180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyInfo" sheetId="7" r:id="rId1"/>
@@ -671,7 +671,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -700,7 +700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="22.05" customHeight="1">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>20</v>
       </c>
@@ -720,7 +720,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22.05" customHeight="1">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>24</v>
       </c>
@@ -740,7 +740,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22.05" customHeight="1">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>27</v>
       </c>
@@ -774,7 +774,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -804,7 +804,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="22.05" customHeight="1">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="14">
         <v>3</v>
       </c>
@@ -815,7 +815,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" s="13">
         <v>3</v>
@@ -824,7 +824,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22.05" customHeight="1">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="14">
         <v>5</v>
       </c>
@@ -835,7 +835,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" s="13">
         <v>3</v>
@@ -844,7 +844,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22.05" customHeight="1">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="14">
         <v>15</v>
       </c>
@@ -855,7 +855,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E4" s="13">
         <v>3</v>
@@ -864,7 +864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22.05" customHeight="1">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="14">
         <v>22</v>
       </c>
@@ -875,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="13">
         <v>2</v>
@@ -884,7 +884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22.05" customHeight="1">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="14">
         <v>28</v>
       </c>
@@ -895,7 +895,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6" s="13">
         <v>4</v>
@@ -904,7 +904,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22.05" customHeight="1">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="14">
         <v>34</v>
       </c>
@@ -915,7 +915,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="13">
         <v>2</v>
@@ -924,7 +924,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22.05" customHeight="1">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="14">
         <v>40</v>
       </c>
@@ -935,7 +935,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="13">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E8" s="13">
         <v>4</v>
@@ -944,7 +944,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22.05" customHeight="1">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="14">
         <v>47</v>
       </c>
@@ -964,7 +964,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22.05" customHeight="1">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="14">
         <v>54</v>
       </c>
@@ -984,7 +984,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22.05" customHeight="1">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="14">
         <v>60</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22.05" customHeight="1">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="14">
         <v>65</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22.05" customHeight="1">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="14">
         <v>71</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22.05" customHeight="1">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="14">
         <v>77</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22.05" customHeight="1">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="14">
         <v>84</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22.05" customHeight="1">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="14">
         <v>90</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22.05" customHeight="1">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="14">
         <v>96</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22.05" customHeight="1">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="14">
         <v>100</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22.05" customHeight="1">
+    <row r="19" spans="1:6" ht="22" customHeight="1">
       <c r="A19" s="14">
         <v>105</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22.05" customHeight="1">
+    <row r="20" spans="1:6" ht="22" customHeight="1">
       <c r="A20" s="14">
         <v>110</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22.05" customHeight="1">
+    <row r="21" spans="1:6" ht="22" customHeight="1">
       <c r="A21" s="14">
         <v>115</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22.05" customHeight="1">
+    <row r="22" spans="1:6" ht="22" customHeight="1">
       <c r="A22" s="14">
         <v>118</v>
       </c>
@@ -1246,7 +1246,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1284,7 +1284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22.05" customHeight="1">
+    <row r="2" spans="1:8" ht="22" customHeight="1">
       <c r="A2" s="17"/>
       <c r="B2" s="18">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22.05" customHeight="1">
+    <row r="3" spans="1:8" ht="22" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="18">
         <v>2</v>
@@ -1334,7 +1334,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22.05" customHeight="1">
+    <row r="4" spans="1:8" ht="22" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="18">
         <v>3</v>
@@ -1359,7 +1359,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22.05" customHeight="1">
+    <row r="5" spans="1:8" ht="22" customHeight="1">
       <c r="A5" s="17"/>
       <c r="B5" s="18">
         <v>4</v>
@@ -1384,7 +1384,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22.05" customHeight="1">
+    <row r="6" spans="1:8" ht="22" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <v>5</v>
@@ -1409,7 +1409,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.05" customHeight="1">
+    <row r="7" spans="1:8" ht="28" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>8</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22.05" customHeight="1">
+    <row r="8" spans="1:8" ht="22" customHeight="1">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1441,7 +1441,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="22.05" customHeight="1">
+    <row r="9" spans="1:8" ht="22" customHeight="1">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1451,7 +1451,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="22.05" customHeight="1">
+    <row r="10" spans="1:8" ht="22" customHeight="1">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1461,7 +1461,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="22.05" customHeight="1">
+    <row r="11" spans="1:8" ht="22" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1471,7 +1471,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="22.05" customHeight="1">
+    <row r="12" spans="1:8" ht="22" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1481,7 +1481,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="22.05" customHeight="1">
+    <row r="13" spans="1:8" ht="22" customHeight="1">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1491,7 +1491,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="22.05" customHeight="1">
+    <row r="14" spans="1:8" ht="22" customHeight="1">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1501,7 +1501,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="22.05" customHeight="1">
+    <row r="15" spans="1:8" ht="22" customHeight="1">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1511,7 +1511,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="22.05" customHeight="1">
+    <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1521,7 +1521,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="22.05" customHeight="1">
+    <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1531,7 +1531,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="22.05" customHeight="1">
+    <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1541,7 +1541,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="22.05" customHeight="1">
+    <row r="19" spans="1:8" ht="22" customHeight="1">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1551,7 +1551,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="22.05" customHeight="1">
+    <row r="20" spans="1:8" ht="22" customHeight="1">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1561,7 +1561,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="22.05" customHeight="1">
+    <row r="21" spans="1:8" ht="22" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1571,7 +1571,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" ht="28.05" customHeight="1">
+    <row r="22" spans="1:8" ht="28" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1590,7 +1590,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1628,7 +1628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22.05" customHeight="1">
+    <row r="2" spans="1:8" ht="22" customHeight="1">
       <c r="A2" s="17"/>
       <c r="B2" s="18">
         <v>1</v>
@@ -1654,7 +1654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22.05" customHeight="1">
+    <row r="3" spans="1:8" ht="22" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="18">
         <v>2</v>
@@ -1680,7 +1680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22.05" customHeight="1">
+    <row r="4" spans="1:8" ht="22" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="18">
         <v>3</v>
@@ -1706,7 +1706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22.05" customHeight="1">
+    <row r="5" spans="1:8" ht="22" customHeight="1">
       <c r="A5" s="17"/>
       <c r="B5" s="18">
         <v>4</v>
@@ -1732,7 +1732,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22.05" customHeight="1">
+    <row r="6" spans="1:8" ht="22" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <v>5</v>
@@ -1758,7 +1758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22.05" customHeight="1">
+    <row r="7" spans="1:8" ht="22" customHeight="1">
       <c r="A7" s="17"/>
       <c r="B7" s="18">
         <v>6</v>
@@ -1784,7 +1784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22.05" customHeight="1">
+    <row r="8" spans="1:8" ht="22" customHeight="1">
       <c r="A8" s="17"/>
       <c r="B8" s="18">
         <v>7</v>
@@ -1810,7 +1810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22.05" customHeight="1">
+    <row r="9" spans="1:8" ht="22" customHeight="1">
       <c r="A9" s="17"/>
       <c r="B9" s="18">
         <v>8</v>
@@ -1836,7 +1836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22.05" customHeight="1">
+    <row r="10" spans="1:8" ht="22" customHeight="1">
       <c r="A10" s="17"/>
       <c r="B10" s="18">
         <v>9</v>
@@ -1862,7 +1862,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22.05" customHeight="1">
+    <row r="11" spans="1:8" ht="22" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="18">
         <v>10</v>
@@ -1888,7 +1888,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22.05" customHeight="1">
+    <row r="12" spans="1:8" ht="22" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="18">
         <v>11</v>
@@ -1914,7 +1914,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="22.05" customHeight="1">
+    <row r="13" spans="1:8" ht="22" customHeight="1">
       <c r="A13" s="17"/>
       <c r="B13" s="18">
         <v>12</v>
@@ -1940,7 +1940,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="22.05" customHeight="1">
+    <row r="14" spans="1:8" ht="22" customHeight="1">
       <c r="A14" s="17"/>
       <c r="B14" s="18">
         <v>13</v>
@@ -1966,7 +1966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="22.05" customHeight="1">
+    <row r="15" spans="1:8" ht="22" customHeight="1">
       <c r="A15" s="17"/>
       <c r="B15" s="18">
         <v>14</v>
@@ -1992,7 +1992,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="22.05" customHeight="1">
+    <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="17"/>
       <c r="B16" s="18">
         <v>15</v>
@@ -2018,7 +2018,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="22.05" customHeight="1">
+    <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="18">
         <v>16</v>
@@ -2044,7 +2044,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="22.05" customHeight="1">
+    <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="17"/>
       <c r="B18" s="18">
         <v>17</v>
@@ -2070,7 +2070,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="22.05" customHeight="1">
+    <row r="19" spans="1:8" ht="22" customHeight="1">
       <c r="A19" s="17"/>
       <c r="B19" s="18">
         <v>18</v>
@@ -2096,7 +2096,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="22.05" customHeight="1">
+    <row r="20" spans="1:8" ht="22" customHeight="1">
       <c r="A20" s="17"/>
       <c r="B20" s="18">
         <v>19</v>
@@ -2122,7 +2122,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="22.05" customHeight="1">
+    <row r="21" spans="1:8" ht="22" customHeight="1">
       <c r="A21" s="17"/>
       <c r="B21" s="18">
         <v>20</v>
@@ -2148,7 +2148,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28.05" customHeight="1">
+    <row r="22" spans="1:8" ht="28" customHeight="1">
       <c r="A22" s="19" t="s">
         <v>8</v>
       </c>
@@ -2179,7 +2179,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -2217,7 +2217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22.05" customHeight="1">
+    <row r="2" spans="1:8" ht="22" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="2">
         <v>1</v>
@@ -2243,7 +2243,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22.05" customHeight="1">
+    <row r="3" spans="1:8" ht="22" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2">
         <v>2</v>
@@ -2269,7 +2269,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22.05" customHeight="1">
+    <row r="4" spans="1:8" ht="22" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="2">
         <v>3</v>
@@ -2295,7 +2295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22.05" customHeight="1">
+    <row r="5" spans="1:8" ht="22" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="2">
         <v>4</v>
@@ -2321,7 +2321,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22.05" customHeight="1">
+    <row r="6" spans="1:8" ht="22" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="2">
         <v>5</v>
@@ -2347,7 +2347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22.05" customHeight="1">
+    <row r="7" spans="1:8" ht="22" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="2">
         <v>6</v>
@@ -2373,7 +2373,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22.05" customHeight="1">
+    <row r="8" spans="1:8" ht="22" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="2">
         <v>7</v>
@@ -2399,7 +2399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22.05" customHeight="1">
+    <row r="9" spans="1:8" ht="22" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="2">
         <v>8</v>
@@ -2425,7 +2425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22.05" customHeight="1">
+    <row r="10" spans="1:8" ht="22" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="2">
         <v>9</v>
@@ -2451,7 +2451,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22.05" customHeight="1">
+    <row r="11" spans="1:8" ht="22" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="2">
         <v>10</v>
@@ -2477,7 +2477,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22.05" customHeight="1">
+    <row r="12" spans="1:8" ht="22" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="2">
         <v>11</v>
@@ -2503,7 +2503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="22.05" customHeight="1">
+    <row r="13" spans="1:8" ht="22" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="2">
         <v>12</v>
@@ -2529,7 +2529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="22.05" customHeight="1">
+    <row r="14" spans="1:8" ht="22" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="2">
         <v>13</v>
@@ -2555,7 +2555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="22.05" customHeight="1">
+    <row r="15" spans="1:8" ht="22" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="2">
         <v>14</v>
@@ -2581,7 +2581,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="22.05" customHeight="1">
+    <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="2">
         <v>15</v>
@@ -2607,7 +2607,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="22.05" customHeight="1">
+    <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="2">
         <v>16</v>
@@ -2633,7 +2633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="22.05" customHeight="1">
+    <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="2">
         <v>17</v>
@@ -2659,7 +2659,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="22.05" customHeight="1">
+    <row r="19" spans="1:8" ht="22" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" s="2">
         <v>18</v>
@@ -2685,7 +2685,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="22.05" customHeight="1">
+    <row r="20" spans="1:8" ht="22" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="2">
         <v>19</v>
@@ -2711,7 +2711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="22.05" customHeight="1">
+    <row r="21" spans="1:8" ht="22" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="2">
         <v>20</v>
@@ -2737,7 +2737,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28.05" customHeight="1">
+    <row r="22" spans="1:8" ht="28" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>

--- a/GameData/GameData_Enemy.xlsx
+++ b/GameData/GameData_Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2663FC7A-66E0-4575-896B-C6601934EC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2077C036-A5FF-429E-AE1B-6993D6C14C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3250" yWindow="3560" windowWidth="20360" windowHeight="13180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3250" yWindow="2100" windowWidth="20360" windowHeight="13180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyInfo" sheetId="7" r:id="rId1"/>
@@ -955,7 +955,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="13">
         <v>3</v>
@@ -975,7 +975,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E10" s="13">
         <v>4</v>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="13">
         <v>1</v>
@@ -1035,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E13" s="13">
         <v>3</v>
@@ -1075,7 +1075,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E15" s="13">
         <v>3</v>
@@ -1095,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E16" s="13">
         <v>5</v>
@@ -1155,7 +1155,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E19" s="13">
         <v>3</v>
@@ -1175,7 +1175,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E20" s="13">
         <v>6</v>

--- a/GameData/GameData_Enemy.xlsx
+++ b/GameData/GameData_Enemy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ac19dd172dbe555/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2077C036-A5FF-429E-AE1B-6993D6C14C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{18AB4CB5-3047-41E0-9822-F30D08F6EBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D59F311-B1B8-4338-A98D-F165170795A1}"/>
   <bookViews>
-    <workbookView xWindow="3250" yWindow="2100" windowWidth="20360" windowHeight="13180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyInfo" sheetId="7" r:id="rId1"/>
@@ -164,9 +164,6 @@
     <t>Interval</t>
   </si>
   <si>
-    <t>x*400</t>
-  </si>
-  <si>
     <t>x*30</t>
   </si>
   <si>
@@ -197,15 +194,19 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>1.9+x*0.1</t>
+    <t>x*250</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>0.8+x*0.2</t>
+    <t>1+x*0.1</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>1+x</t>
+    <t>0.3+x*0.1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1+x0.4</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -671,7 +672,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -700,7 +701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1">
+    <row r="2" spans="1:6" ht="22.05" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>20</v>
       </c>
@@ -720,7 +721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1">
+    <row r="3" spans="1:6" ht="22.05" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>24</v>
       </c>
@@ -734,13 +735,13 @@
         <v>26</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="13">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1">
+    <row r="4" spans="1:6" ht="22.05" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>27</v>
       </c>
@@ -774,7 +775,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -804,7 +805,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1">
+    <row r="2" spans="1:6" ht="22.05" customHeight="1">
       <c r="A2" s="14">
         <v>3</v>
       </c>
@@ -818,13 +819,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" s="15">
         <v>1.2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1">
+    <row r="3" spans="1:6" ht="22.05" customHeight="1">
       <c r="A3" s="14">
         <v>5</v>
       </c>
@@ -844,7 +845,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1">
+    <row r="4" spans="1:6" ht="22.05" customHeight="1">
       <c r="A4" s="14">
         <v>15</v>
       </c>
@@ -852,19 +853,19 @@
         <v>24</v>
       </c>
       <c r="C4" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="13">
         <v>3</v>
       </c>
       <c r="E4" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1">
+    <row r="5" spans="1:6" ht="22.05" customHeight="1">
       <c r="A5" s="14">
         <v>22</v>
       </c>
@@ -878,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1">
+    <row r="6" spans="1:6" ht="22.05" customHeight="1">
       <c r="A6" s="14">
         <v>28</v>
       </c>
@@ -892,19 +893,19 @@
         <v>20</v>
       </c>
       <c r="C6" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="13">
         <v>2</v>
       </c>
       <c r="E6" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="15">
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1">
+    <row r="7" spans="1:6" ht="22.05" customHeight="1">
       <c r="A7" s="14">
         <v>34</v>
       </c>
@@ -912,19 +913,19 @@
         <v>24</v>
       </c>
       <c r="C7" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="13">
         <v>3</v>
       </c>
       <c r="E7" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="15">
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1">
+    <row r="8" spans="1:6" ht="22.05" customHeight="1">
       <c r="A8" s="14">
         <v>40</v>
       </c>
@@ -932,19 +933,19 @@
         <v>20</v>
       </c>
       <c r="C8" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" s="13">
         <v>4</v>
       </c>
       <c r="E8" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="15">
         <v>0.8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1">
+    <row r="9" spans="1:6" ht="22.05" customHeight="1">
       <c r="A9" s="14">
         <v>47</v>
       </c>
@@ -952,19 +953,19 @@
         <v>24</v>
       </c>
       <c r="C9" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="13">
         <v>5</v>
       </c>
       <c r="E9" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="15">
         <v>1.4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1">
+    <row r="10" spans="1:6" ht="22.05" customHeight="1">
       <c r="A10" s="14">
         <v>54</v>
       </c>
@@ -972,19 +973,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="13">
+        <v>4</v>
+      </c>
+      <c r="D10" s="13">
         <v>5</v>
       </c>
-      <c r="D10" s="13">
-        <v>4</v>
-      </c>
       <c r="E10" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="15">
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1">
+    <row r="11" spans="1:6" ht="22.05" customHeight="1">
       <c r="A11" s="14">
         <v>60</v>
       </c>
@@ -995,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" s="13">
         <v>1</v>
@@ -1004,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1">
+    <row r="12" spans="1:6" ht="22.05" customHeight="1">
       <c r="A12" s="14">
         <v>65</v>
       </c>
@@ -1012,19 +1013,19 @@
         <v>20</v>
       </c>
       <c r="C12" s="13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" s="13">
         <v>2</v>
       </c>
       <c r="E12" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="15">
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1">
+    <row r="13" spans="1:6" ht="22.05" customHeight="1">
       <c r="A13" s="14">
         <v>71</v>
       </c>
@@ -1032,19 +1033,19 @@
         <v>24</v>
       </c>
       <c r="C13" s="13">
+        <v>3</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2</v>
+      </c>
+      <c r="E13" s="13">
         <v>4</v>
-      </c>
-      <c r="D13" s="13">
-        <v>4</v>
-      </c>
-      <c r="E13" s="13">
-        <v>3</v>
       </c>
       <c r="F13" s="15">
         <v>1.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1">
+    <row r="14" spans="1:6" ht="22.05" customHeight="1">
       <c r="A14" s="14">
         <v>77</v>
       </c>
@@ -1052,19 +1053,19 @@
         <v>20</v>
       </c>
       <c r="C14" s="13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D14" s="13">
         <v>4</v>
       </c>
       <c r="E14" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="15">
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1">
+    <row r="15" spans="1:6" ht="22.05" customHeight="1">
       <c r="A15" s="14">
         <v>84</v>
       </c>
@@ -1072,19 +1073,19 @@
         <v>24</v>
       </c>
       <c r="C15" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1">
+    <row r="16" spans="1:6" ht="22.05" customHeight="1">
       <c r="A16" s="14">
         <v>90</v>
       </c>
@@ -1092,39 +1093,39 @@
         <v>20</v>
       </c>
       <c r="C16" s="13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D16" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="15">
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1">
+    <row r="17" spans="1:6" ht="22.05" customHeight="1">
       <c r="A17" s="14">
         <v>96</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C17" s="13">
+        <v>4</v>
+      </c>
+      <c r="D17" s="13">
+        <v>1</v>
+      </c>
+      <c r="E17" s="13">
         <v>2</v>
-      </c>
-      <c r="D17" s="13">
-        <v>1</v>
-      </c>
-      <c r="E17" s="13">
-        <v>1</v>
       </c>
       <c r="F17" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1">
+    <row r="18" spans="1:6" ht="22.05" customHeight="1">
       <c r="A18" s="14">
         <v>100</v>
       </c>
@@ -1132,19 +1133,19 @@
         <v>20</v>
       </c>
       <c r="C18" s="13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D18" s="13">
         <v>3</v>
       </c>
       <c r="E18" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="15">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1">
+    <row r="19" spans="1:6" ht="22.05" customHeight="1">
       <c r="A19" s="14">
         <v>105</v>
       </c>
@@ -1152,19 +1153,19 @@
         <v>24</v>
       </c>
       <c r="C19" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E19" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="15">
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1">
+    <row r="20" spans="1:6" ht="22.05" customHeight="1">
       <c r="A20" s="14">
         <v>110</v>
       </c>
@@ -1172,19 +1173,19 @@
         <v>20</v>
       </c>
       <c r="C20" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D20" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="15">
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1">
+    <row r="21" spans="1:6" ht="22.05" customHeight="1">
       <c r="A21" s="14">
         <v>115</v>
       </c>
@@ -1192,19 +1193,19 @@
         <v>24</v>
       </c>
       <c r="C21" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D21" s="13">
         <v>2</v>
       </c>
       <c r="E21" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" s="15">
         <v>0.8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1">
+    <row r="22" spans="1:6" ht="22.05" customHeight="1">
       <c r="A22" s="14">
         <v>118</v>
       </c>
@@ -1212,13 +1213,13 @@
         <v>27</v>
       </c>
       <c r="C22" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="15">
         <v>0</v>
@@ -1246,7 +1247,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1284,13 +1285,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22" customHeight="1">
+    <row r="2" spans="1:8" ht="22.05" customHeight="1">
       <c r="A2" s="17"/>
       <c r="B2" s="18">
         <v>1</v>
       </c>
       <c r="C2" s="21">
-        <v>400</v>
+        <f>B2*250</f>
+        <v>250</v>
       </c>
       <c r="D2" s="22">
         <v>30</v>
@@ -1302,20 +1304,21 @@
         <v>1</v>
       </c>
       <c r="G2" s="22">
-        <f>1+B2</f>
-        <v>2</v>
+        <f>0.1+B2*0.4</f>
+        <v>0.5</v>
       </c>
       <c r="H2" s="21">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22" customHeight="1">
+    <row r="3" spans="1:8" ht="22.05" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="18">
         <v>2</v>
       </c>
       <c r="C3" s="21">
-        <v>800</v>
+        <f t="shared" ref="C3:C6" si="0">B3*250</f>
+        <v>500</v>
       </c>
       <c r="D3" s="22">
         <v>60</v>
@@ -1327,20 +1330,21 @@
         <v>1</v>
       </c>
       <c r="G3" s="22">
-        <f t="shared" ref="G3:G6" si="0">1+B3</f>
-        <v>3</v>
+        <f t="shared" ref="G3:G6" si="1">0.1+B3*0.4</f>
+        <v>0.9</v>
       </c>
       <c r="H3" s="21">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22" customHeight="1">
+    <row r="4" spans="1:8" ht="22.05" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="18">
         <v>3</v>
       </c>
       <c r="C4" s="21">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>750</v>
       </c>
       <c r="D4" s="22">
         <v>90</v>
@@ -1352,20 +1356,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>1.3000000000000003</v>
       </c>
       <c r="H4" s="21">
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22" customHeight="1">
+    <row r="5" spans="1:8" ht="22.05" customHeight="1">
       <c r="A5" s="17"/>
       <c r="B5" s="18">
         <v>4</v>
       </c>
       <c r="C5" s="21">
-        <v>1600</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
       <c r="D5" s="22">
         <v>120</v>
@@ -1377,20 +1382,21 @@
         <v>1</v>
       </c>
       <c r="G5" s="22">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>1.7000000000000002</v>
       </c>
       <c r="H5" s="21">
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22" customHeight="1">
+    <row r="6" spans="1:8" ht="22.05" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <v>5</v>
       </c>
       <c r="C6" s="21">
-        <v>2000</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="D6" s="22">
         <v>150</v>
@@ -1402,36 +1408,36 @@
         <v>1</v>
       </c>
       <c r="G6" s="22">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>2.1</v>
       </c>
       <c r="H6" s="21">
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28" customHeight="1">
+    <row r="7" spans="1:8" ht="28.05" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="20"/>
-      <c r="C7" s="20" t="s" cm="1">
+      <c r="C7" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="20" t="s" cm="1">
         <v>35</v>
       </c>
-      <c r="D7" s="20" t="s" cm="1">
+      <c r="E7" s="20" t="s" cm="1">
         <v>36</v>
-      </c>
-      <c r="E7" s="20" t="s" cm="1">
-        <v>37</v>
       </c>
       <c r="F7" s="20"/>
       <c r="G7" s="20" t="s">
         <v>47</v>
       </c>
       <c r="H7" s="20" t="s" cm="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="22" customHeight="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="22.05" customHeight="1">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1441,7 +1447,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="22" customHeight="1">
+    <row r="9" spans="1:8" ht="22.05" customHeight="1">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1451,7 +1457,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="22" customHeight="1">
+    <row r="10" spans="1:8" ht="22.05" customHeight="1">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1461,7 +1467,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="22" customHeight="1">
+    <row r="11" spans="1:8" ht="22.05" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1471,7 +1477,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="22" customHeight="1">
+    <row r="12" spans="1:8" ht="22.05" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1481,7 +1487,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="22" customHeight="1">
+    <row r="13" spans="1:8" ht="22.05" customHeight="1">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1491,7 +1497,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="22" customHeight="1">
+    <row r="14" spans="1:8" ht="22.05" customHeight="1">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1501,7 +1507,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1">
+    <row r="15" spans="1:8" ht="22.05" customHeight="1">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1511,7 +1517,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1">
+    <row r="16" spans="1:8" ht="22.05" customHeight="1">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1521,7 +1527,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
+    <row r="17" spans="1:8" ht="22.05" customHeight="1">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1531,7 +1537,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="22" customHeight="1">
+    <row r="18" spans="1:8" ht="22.05" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1541,7 +1547,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="22" customHeight="1">
+    <row r="19" spans="1:8" ht="22.05" customHeight="1">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1551,7 +1557,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="22" customHeight="1">
+    <row r="20" spans="1:8" ht="22.05" customHeight="1">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1561,7 +1567,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="22" customHeight="1">
+    <row r="21" spans="1:8" ht="22.05" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1571,7 +1577,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" ht="28" customHeight="1">
+    <row r="22" spans="1:8" ht="28.05" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1590,7 +1596,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1628,7 +1634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22" customHeight="1">
+    <row r="2" spans="1:8" ht="22.05" customHeight="1">
       <c r="A2" s="17"/>
       <c r="B2" s="18">
         <v>1</v>
@@ -1647,14 +1653,14 @@
         <v>8</v>
       </c>
       <c r="G2" s="22">
-        <f>0.8+B2*0.2</f>
-        <v>1</v>
+        <f>0.3+B2*0.1</f>
+        <v>0.4</v>
       </c>
       <c r="H2" s="21">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22" customHeight="1">
+    <row r="3" spans="1:8" ht="22.05" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="18">
         <v>2</v>
@@ -1673,14 +1679,14 @@
         <v>8</v>
       </c>
       <c r="G3" s="22">
-        <f t="shared" ref="G3:G21" si="1">0.8+B3*0.2</f>
-        <v>1.2000000000000002</v>
+        <f t="shared" ref="G3:G21" si="1">0.3+B3*0.1</f>
+        <v>0.5</v>
       </c>
       <c r="H3" s="21">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22" customHeight="1">
+    <row r="4" spans="1:8" ht="22.05" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="18">
         <v>3</v>
@@ -1700,13 +1706,13 @@
       </c>
       <c r="G4" s="22">
         <f t="shared" si="1"/>
-        <v>1.4000000000000001</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="H4" s="21">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22" customHeight="1">
+    <row r="5" spans="1:8" ht="22.05" customHeight="1">
       <c r="A5" s="17"/>
       <c r="B5" s="18">
         <v>4</v>
@@ -1726,13 +1732,13 @@
       </c>
       <c r="G5" s="22">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="H5" s="21">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22" customHeight="1">
+    <row r="6" spans="1:8" ht="22.05" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <v>5</v>
@@ -1752,13 +1758,13 @@
       </c>
       <c r="G6" s="22">
         <f t="shared" si="1"/>
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="21">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22" customHeight="1">
+    <row r="7" spans="1:8" ht="22.05" customHeight="1">
       <c r="A7" s="17"/>
       <c r="B7" s="18">
         <v>6</v>
@@ -1778,13 +1784,13 @@
       </c>
       <c r="G7" s="22">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="H7" s="21">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22" customHeight="1">
+    <row r="8" spans="1:8" ht="22.05" customHeight="1">
       <c r="A8" s="17"/>
       <c r="B8" s="18">
         <v>7</v>
@@ -1804,13 +1810,13 @@
       </c>
       <c r="G8" s="22">
         <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="H8" s="21">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22" customHeight="1">
+    <row r="9" spans="1:8" ht="22.05" customHeight="1">
       <c r="A9" s="17"/>
       <c r="B9" s="18">
         <v>8</v>
@@ -1830,13 +1836,13 @@
       </c>
       <c r="G9" s="22">
         <f t="shared" si="1"/>
-        <v>2.4000000000000004</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H9" s="21">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22" customHeight="1">
+    <row r="10" spans="1:8" ht="22.05" customHeight="1">
       <c r="A10" s="17"/>
       <c r="B10" s="18">
         <v>9</v>
@@ -1856,13 +1862,13 @@
       </c>
       <c r="G10" s="22">
         <f t="shared" si="1"/>
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="H10" s="21">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22" customHeight="1">
+    <row r="11" spans="1:8" ht="22.05" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="18">
         <v>10</v>
@@ -1882,13 +1888,13 @@
       </c>
       <c r="G11" s="22">
         <f t="shared" si="1"/>
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="H11" s="21">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22" customHeight="1">
+    <row r="12" spans="1:8" ht="22.05" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="18">
         <v>11</v>
@@ -1908,13 +1914,13 @@
       </c>
       <c r="G12" s="22">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="H12" s="21">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="22" customHeight="1">
+    <row r="13" spans="1:8" ht="22.05" customHeight="1">
       <c r="A13" s="17"/>
       <c r="B13" s="18">
         <v>12</v>
@@ -1934,13 +1940,13 @@
       </c>
       <c r="G13" s="22">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>1.5000000000000002</v>
       </c>
       <c r="H13" s="21">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="22" customHeight="1">
+    <row r="14" spans="1:8" ht="22.05" customHeight="1">
       <c r="A14" s="17"/>
       <c r="B14" s="18">
         <v>13</v>
@@ -1960,13 +1966,13 @@
       </c>
       <c r="G14" s="22">
         <f t="shared" si="1"/>
-        <v>3.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="H14" s="21">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1">
+    <row r="15" spans="1:8" ht="22.05" customHeight="1">
       <c r="A15" s="17"/>
       <c r="B15" s="18">
         <v>14</v>
@@ -1986,13 +1992,13 @@
       </c>
       <c r="G15" s="22">
         <f t="shared" si="1"/>
-        <v>3.6000000000000005</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="H15" s="21">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1">
+    <row r="16" spans="1:8" ht="22.05" customHeight="1">
       <c r="A16" s="17"/>
       <c r="B16" s="18">
         <v>15</v>
@@ -2012,13 +2018,13 @@
       </c>
       <c r="G16" s="22">
         <f t="shared" si="1"/>
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="H16" s="21">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
+    <row r="17" spans="1:8" ht="22.05" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="18">
         <v>16</v>
@@ -2038,13 +2044,13 @@
       </c>
       <c r="G17" s="22">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>1.9000000000000001</v>
       </c>
       <c r="H17" s="21">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="22" customHeight="1">
+    <row r="18" spans="1:8" ht="22.05" customHeight="1">
       <c r="A18" s="17"/>
       <c r="B18" s="18">
         <v>17</v>
@@ -2064,13 +2070,13 @@
       </c>
       <c r="G18" s="22">
         <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="H18" s="21">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="22" customHeight="1">
+    <row r="19" spans="1:8" ht="22.05" customHeight="1">
       <c r="A19" s="17"/>
       <c r="B19" s="18">
         <v>18</v>
@@ -2090,13 +2096,13 @@
       </c>
       <c r="G19" s="22">
         <f t="shared" si="1"/>
-        <v>4.4000000000000004</v>
+        <v>2.1</v>
       </c>
       <c r="H19" s="21">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="22" customHeight="1">
+    <row r="20" spans="1:8" ht="22.05" customHeight="1">
       <c r="A20" s="17"/>
       <c r="B20" s="18">
         <v>19</v>
@@ -2116,13 +2122,13 @@
       </c>
       <c r="G20" s="22">
         <f t="shared" si="1"/>
-        <v>4.6000000000000005</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H20" s="21">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="22" customHeight="1">
+    <row r="21" spans="1:8" ht="22.05" customHeight="1">
       <c r="A21" s="17"/>
       <c r="B21" s="18">
         <v>20</v>
@@ -2142,32 +2148,32 @@
       </c>
       <c r="G21" s="22">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H21" s="21">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28" customHeight="1">
+    <row r="22" spans="1:8" ht="28.05" customHeight="1">
       <c r="A22" s="19" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="20" t="s" cm="1">
+        <v>38</v>
+      </c>
+      <c r="E22" s="20" t="s" cm="1">
         <v>39</v>
-      </c>
-      <c r="E22" s="20" t="s" cm="1">
-        <v>40</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20" t="s">
         <v>46</v>
       </c>
       <c r="H22" s="20" t="s" cm="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2179,7 +2185,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -2217,7 +2223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22" customHeight="1">
+    <row r="2" spans="1:8" ht="22.05" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="2">
         <v>1</v>
@@ -2236,14 +2242,14 @@
         <v>1</v>
       </c>
       <c r="G2" s="9">
-        <f>1.9+B2*0.1</f>
-        <v>2</v>
+        <f>1+B2*0.1</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H2" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="22" customHeight="1">
+    <row r="3" spans="1:8" ht="22.05" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2">
         <v>2</v>
@@ -2262,14 +2268,14 @@
         <v>1</v>
       </c>
       <c r="G3" s="9">
-        <f t="shared" ref="G3:G21" si="1">1.9+B3*0.1</f>
-        <v>2.1</v>
+        <f t="shared" ref="G3:G21" si="1">1+B3*0.1</f>
+        <v>1.2</v>
       </c>
       <c r="H3" s="8">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="22" customHeight="1">
+    <row r="4" spans="1:8" ht="22.05" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="2">
         <v>3</v>
@@ -2289,13 +2295,13 @@
       </c>
       <c r="G4" s="9">
         <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
+        <v>1.3</v>
       </c>
       <c r="H4" s="8">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22" customHeight="1">
+    <row r="5" spans="1:8" ht="22.05" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="2">
         <v>4</v>
@@ -2315,13 +2321,13 @@
       </c>
       <c r="G5" s="9">
         <f t="shared" si="1"/>
-        <v>2.2999999999999998</v>
+        <v>1.4</v>
       </c>
       <c r="H5" s="8">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22" customHeight="1">
+    <row r="6" spans="1:8" ht="22.05" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="2">
         <v>5</v>
@@ -2341,13 +2347,13 @@
       </c>
       <c r="G6" s="9">
         <f t="shared" si="1"/>
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="8">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22" customHeight="1">
+    <row r="7" spans="1:8" ht="22.05" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="2">
         <v>6</v>
@@ -2367,13 +2373,13 @@
       </c>
       <c r="G7" s="9">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="H7" s="8">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22" customHeight="1">
+    <row r="8" spans="1:8" ht="22.05" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="2">
         <v>7</v>
@@ -2393,13 +2399,13 @@
       </c>
       <c r="G8" s="9">
         <f t="shared" si="1"/>
-        <v>2.6</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="H8" s="8">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22" customHeight="1">
+    <row r="9" spans="1:8" ht="22.05" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="2">
         <v>8</v>
@@ -2419,13 +2425,13 @@
       </c>
       <c r="G9" s="9">
         <f t="shared" si="1"/>
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="H9" s="8">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22" customHeight="1">
+    <row r="10" spans="1:8" ht="22.05" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="2">
         <v>9</v>
@@ -2445,13 +2451,13 @@
       </c>
       <c r="G10" s="9">
         <f t="shared" si="1"/>
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="H10" s="8">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22" customHeight="1">
+    <row r="11" spans="1:8" ht="22.05" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="2">
         <v>10</v>
@@ -2471,13 +2477,13 @@
       </c>
       <c r="G11" s="9">
         <f t="shared" si="1"/>
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="H11" s="8">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22" customHeight="1">
+    <row r="12" spans="1:8" ht="22.05" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="2">
         <v>11</v>
@@ -2497,13 +2503,13 @@
       </c>
       <c r="G12" s="9">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="H12" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="22" customHeight="1">
+    <row r="13" spans="1:8" ht="22.05" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="2">
         <v>12</v>
@@ -2523,13 +2529,13 @@
       </c>
       <c r="G13" s="9">
         <f t="shared" si="1"/>
-        <v>3.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H13" s="8">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="22" customHeight="1">
+    <row r="14" spans="1:8" ht="22.05" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="2">
         <v>13</v>
@@ -2549,13 +2555,13 @@
       </c>
       <c r="G14" s="9">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H14" s="8">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1">
+    <row r="15" spans="1:8" ht="22.05" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="2">
         <v>14</v>
@@ -2575,13 +2581,13 @@
       </c>
       <c r="G15" s="9">
         <f t="shared" si="1"/>
-        <v>3.3</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="H15" s="8">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1">
+    <row r="16" spans="1:8" ht="22.05" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="2">
         <v>15</v>
@@ -2601,13 +2607,13 @@
       </c>
       <c r="G16" s="9">
         <f t="shared" si="1"/>
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="H16" s="8">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
+    <row r="17" spans="1:8" ht="22.05" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="2">
         <v>16</v>
@@ -2627,13 +2633,13 @@
       </c>
       <c r="G17" s="9">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="H17" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="22" customHeight="1">
+    <row r="18" spans="1:8" ht="22.05" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="2">
         <v>17</v>
@@ -2653,13 +2659,13 @@
       </c>
       <c r="G18" s="9">
         <f t="shared" si="1"/>
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="H18" s="8">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="22" customHeight="1">
+    <row r="19" spans="1:8" ht="22.05" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" s="2">
         <v>18</v>
@@ -2679,13 +2685,13 @@
       </c>
       <c r="G19" s="9">
         <f t="shared" si="1"/>
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="H19" s="8">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="22" customHeight="1">
+    <row r="20" spans="1:8" ht="22.05" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="2">
         <v>19</v>
@@ -2705,13 +2711,13 @@
       </c>
       <c r="G20" s="9">
         <f t="shared" si="1"/>
-        <v>3.8</v>
+        <v>2.9000000000000004</v>
       </c>
       <c r="H20" s="8">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="22" customHeight="1">
+    <row r="21" spans="1:8" ht="22.05" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="2">
         <v>20</v>
@@ -2731,19 +2737,19 @@
       </c>
       <c r="G21" s="9">
         <f t="shared" si="1"/>
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="H21" s="8">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28" customHeight="1">
+    <row r="22" spans="1:8" ht="28.05" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>11</v>

--- a/GameData/GameData_Enemy.xlsx
+++ b/GameData/GameData_Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ac19dd172dbe555/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{18AB4CB5-3047-41E0-9822-F30D08F6EBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D59F311-B1B8-4338-A98D-F165170795A1}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{22E32C19-D0CA-44ED-B0D1-8162B459303D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10ABC991-FD50-46C1-9281-43B2956B7F68}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="48">
   <si>
     <t>보스</t>
   </si>
@@ -774,7 +774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1222,6 +1222,406 @@
         <v>2</v>
       </c>
       <c r="F22" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="14">
+        <v>130</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="13">
+        <v>6</v>
+      </c>
+      <c r="D23" s="13">
+        <v>5</v>
+      </c>
+      <c r="E23" s="13">
+        <v>3</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="14">
+        <v>132</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="13">
+        <v>6</v>
+      </c>
+      <c r="D24" s="13">
+        <v>5</v>
+      </c>
+      <c r="E24" s="13">
+        <v>4</v>
+      </c>
+      <c r="F24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="14">
+        <v>138</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="13">
+        <v>6</v>
+      </c>
+      <c r="D25" s="13">
+        <v>5</v>
+      </c>
+      <c r="E25" s="13">
+        <v>3</v>
+      </c>
+      <c r="F25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="14">
+        <v>139</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="13">
+        <v>6</v>
+      </c>
+      <c r="D26" s="13">
+        <v>5</v>
+      </c>
+      <c r="E26" s="13">
+        <v>4</v>
+      </c>
+      <c r="F26" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="14">
+        <v>140</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="13">
+        <v>6</v>
+      </c>
+      <c r="D27" s="13">
+        <v>5</v>
+      </c>
+      <c r="E27" s="13">
+        <v>3</v>
+      </c>
+      <c r="F27" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="14">
+        <v>142</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="13">
+        <v>7</v>
+      </c>
+      <c r="D28" s="13">
+        <v>5</v>
+      </c>
+      <c r="E28" s="13">
+        <v>4</v>
+      </c>
+      <c r="F28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="14">
+        <v>148</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="13">
+        <v>7</v>
+      </c>
+      <c r="D29" s="13">
+        <v>5</v>
+      </c>
+      <c r="E29" s="13">
+        <v>3</v>
+      </c>
+      <c r="F29" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="14">
+        <v>146</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="13">
+        <v>7</v>
+      </c>
+      <c r="D30" s="13">
+        <v>5</v>
+      </c>
+      <c r="E30" s="13">
+        <v>4</v>
+      </c>
+      <c r="F30" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="14">
+        <v>149</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="13">
+        <v>7</v>
+      </c>
+      <c r="D31" s="13">
+        <v>5</v>
+      </c>
+      <c r="E31" s="13">
+        <v>5</v>
+      </c>
+      <c r="F31" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="14">
+        <v>150</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="13">
+        <v>2</v>
+      </c>
+      <c r="D32" s="13">
+        <v>5</v>
+      </c>
+      <c r="E32" s="13">
+        <v>1</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="14">
+        <v>157</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="13">
+        <v>6</v>
+      </c>
+      <c r="D33" s="13">
+        <v>5</v>
+      </c>
+      <c r="E33" s="13">
+        <v>6</v>
+      </c>
+      <c r="F33" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="14">
+        <v>160</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="13">
+        <v>6</v>
+      </c>
+      <c r="D34" s="13">
+        <v>5</v>
+      </c>
+      <c r="E34" s="13">
+        <v>6</v>
+      </c>
+      <c r="F34" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="14">
+        <v>161</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="13">
+        <v>7</v>
+      </c>
+      <c r="D35" s="13">
+        <v>5</v>
+      </c>
+      <c r="E35" s="13">
+        <v>3</v>
+      </c>
+      <c r="F35" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="14">
+        <v>163</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="13">
+        <v>7</v>
+      </c>
+      <c r="D36" s="13">
+        <v>5</v>
+      </c>
+      <c r="E36" s="13">
+        <v>4</v>
+      </c>
+      <c r="F36" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="14">
+        <v>164</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="13">
+        <v>7</v>
+      </c>
+      <c r="D37" s="13">
+        <v>5</v>
+      </c>
+      <c r="E37" s="13">
+        <v>4</v>
+      </c>
+      <c r="F37" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="14">
+        <v>165</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="13">
+        <v>8</v>
+      </c>
+      <c r="D38" s="13">
+        <v>5</v>
+      </c>
+      <c r="E38" s="13">
+        <v>4</v>
+      </c>
+      <c r="F38" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="14">
+        <v>166</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="13">
+        <v>8</v>
+      </c>
+      <c r="D39" s="13">
+        <v>5</v>
+      </c>
+      <c r="E39" s="13">
+        <v>4</v>
+      </c>
+      <c r="F39" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="14">
+        <v>170</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="13">
+        <v>10</v>
+      </c>
+      <c r="D40" s="13">
+        <v>5</v>
+      </c>
+      <c r="E40" s="13">
+        <v>2</v>
+      </c>
+      <c r="F40" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="14">
+        <v>179</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="13">
+        <v>10</v>
+      </c>
+      <c r="D41" s="13">
+        <v>5</v>
+      </c>
+      <c r="E41" s="13">
+        <v>2</v>
+      </c>
+      <c r="F41" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="14">
+        <v>180</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="13">
+        <v>3</v>
+      </c>
+      <c r="D42" s="13">
+        <v>5</v>
+      </c>
+      <c r="E42" s="13">
+        <v>1</v>
+      </c>
+      <c r="F42" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1231,7 +1631,7 @@
     <dataValidation type="list" sqref="B2:B100" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"skeleton,goblin_mage,boss"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="C2:C100 E2:E100" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" sqref="E2:E100 C2:C100" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
